--- a/resources/TIER/Tier Summary.xlsx
+++ b/resources/TIER/Tier Summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/resources/TIER/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FED5F5D-50A6-F84C-81AE-1EC42B6C714A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="8_{7FED5F5D-50A6-F84C-81AE-1EC42B6C714A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92838939-30D7-4D44-9337-A153EF13E0E0}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="1500" windowWidth="27240" windowHeight="15020" activeTab="3" xr2:uid="{F61A66A6-2BB4-B445-8D7A-81B0E2BBFC2C}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   <externalReferences>
     <externalReference r:id="rId5"/>
   </externalReferences>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="236">
   <si>
     <t>HIV programme area</t>
   </si>
@@ -1317,20 +1317,95 @@
     <t>Although its more viral suppression that does</t>
   </si>
   <si>
-    <t>Generally, I looked at scenario 3 and took most minimums and some standards</t>
-  </si>
-  <si>
-    <t>Also grouped some into broader packages</t>
-  </si>
-  <si>
     <t>Impact will differ based on prevalence</t>
+  </si>
+  <si>
+    <t>Not sure if VL can bre broken down?</t>
+  </si>
+  <si>
+    <t>Generally, I looked at scenario 3 and took most minimums and some standards. Also grouped some into broader packages</t>
+  </si>
+  <si>
+    <t>Phone tracing</t>
+  </si>
+  <si>
+    <t>Home Tracing</t>
+  </si>
+  <si>
+    <t>Maybe could exclude? Just do tracing total</t>
+  </si>
+  <si>
+    <t>I'm not quite sure the best way to handle the lab tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conduct CD4 testing </t>
+  </si>
+  <si>
+    <t>Crag I think</t>
+  </si>
+  <si>
+    <t>Mental Health support</t>
+  </si>
+  <si>
+    <t>Adherence counselling</t>
+  </si>
+  <si>
+    <t>Facility patient education</t>
+  </si>
+  <si>
+    <t>HIV testing</t>
+  </si>
+  <si>
+    <t>EID</t>
+  </si>
+  <si>
+    <t>HIVST</t>
+  </si>
+  <si>
+    <t>Not sure whether to rather do these like your interventions?</t>
+  </si>
+  <si>
+    <t>Significant grouping of the TIER ones</t>
+  </si>
+  <si>
+    <t>Key populations and STI</t>
+  </si>
+  <si>
+    <t>I separated some of the ANC services out? Maybe only EID?</t>
+  </si>
+  <si>
+    <t>PrEP initiation and continuation</t>
+  </si>
+  <si>
+    <t>Oral</t>
+  </si>
+  <si>
+    <t>Cab-LA</t>
+  </si>
+  <si>
+    <t>Lenacapavir</t>
+  </si>
+  <si>
+    <t>Harm reduction for people who inject drugs (facility based or existing KP services)</t>
+  </si>
+  <si>
+    <t>Condom Availability</t>
+  </si>
+  <si>
+    <t>PEP (facility based, GBV and KP services)</t>
+  </si>
+  <si>
+    <t>VMMC (esp. areas with high HIV prev and low circumcision prev)</t>
+  </si>
+  <si>
+    <t>Setting dependent</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1398,6 +1473,19 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -1920,35 +2008,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1960,15 +2027,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1981,27 +2039,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2010,35 +2053,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2049,59 +2071,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2112,27 +2089,23 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2147,33 +2120,164 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="15">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDCD2C3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF5F0E5"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2192,6 +2296,20 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF08BDBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDCD2C3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF5F0E5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2298,8 +2416,8 @@
       <sheetName val="ANNEX 3 PREVENTION"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2">
         <row r="6">
           <cell r="B6" t="str">
@@ -2334,17 +2452,21 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
       <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2677,48 +2799,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="78" t="s">
+      <c r="H1" s="37" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="3" t="str">
+      <c r="A2" s="88"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="1" t="str">
         <f>'[1]Scenario overview'!B6</f>
         <v>A high-burden country close to reaching 95s across all populations</v>
       </c>
-      <c r="E2" s="3" t="str">
+      <c r="E2" s="1" t="str">
         <f>'[1]Scenario overview'!B7</f>
         <v>A high-burden country close to reaching 95s, but not in all populations</v>
       </c>
-      <c r="F2" s="3" t="str">
+      <c r="F2" s="1" t="str">
         <f>'[1]Scenario overview'!B8</f>
         <v>A high-burden country not yet achieving one or more of the 95s</v>
       </c>
-      <c r="G2" s="3" t="str">
+      <c r="G2" s="1" t="str">
         <f>'[1]Scenario overview'!B9</f>
         <v>A low-burden country achieving one or more of the 95s</v>
       </c>
@@ -2727,1351 +2849,1354 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5" t="str">
+      <c r="A3" s="88"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="2" t="str">
         <f>'[1]Scenario overview'!C6</f>
         <v>Limited, possibly some unsuppressed ART clients and some specific sub-segments that are generally underserved</v>
       </c>
-      <c r="E3" s="5" t="str">
+      <c r="E3" s="2" t="str">
         <f>'[1]Scenario overview'!C7</f>
         <v>Adolescent girls and young women, key populations, men</v>
       </c>
-      <c r="F3" s="5" t="str">
+      <c r="F3" s="2" t="str">
         <f>'[1]Scenario overview'!C8</f>
         <v>Clinically unstable/symptomatic, gaps in all population groups</v>
       </c>
-      <c r="G3" s="5" t="str">
+      <c r="G3" s="2" t="str">
         <f>'[1]Scenario overview'!C9</f>
         <v>Clinically unstable/symptomatic, gaps in all population groups</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="45" x14ac:dyDescent="0.2">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H4" s="79" t="s">
+      <c r="D4" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H4" s="38" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="75" x14ac:dyDescent="0.2">
-      <c r="A5" s="28"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12" t="s">
+      <c r="A5" s="78"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="H5" s="79" t="s">
+      <c r="D5" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" s="38" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.2">
-      <c r="A6" s="28"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="12" t="s">
+      <c r="A6" s="78"/>
+      <c r="B6" s="81"/>
+      <c r="C6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" s="13" t="s">
+      <c r="D6" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="A7" s="28"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="12" t="s">
+      <c r="A7" s="78"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="H7" s="79" t="s">
+      <c r="D7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" s="38" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="A8" s="28"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="14" t="s">
+      <c r="A8" s="78"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="H8" s="88" t="s">
+      <c r="D8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" s="42" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="A9" s="28"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="14" t="s">
+      <c r="A9" s="78"/>
+      <c r="B9" s="81"/>
+      <c r="C9" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="H9" s="88" t="s">
+      <c r="D9" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" s="42" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="14" t="s">
+      <c r="A10" s="78"/>
+      <c r="B10" s="81"/>
+      <c r="C10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="H10" s="88" t="s">
+      <c r="D10" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" s="42" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="45" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="14" t="s">
+      <c r="A11" s="78"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="H11" s="88" t="s">
+      <c r="D11" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="42" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="14" t="s">
+      <c r="A12" s="78"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="H12" s="88" t="s">
+      <c r="D12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" s="42" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="14" t="s">
+      <c r="A13" s="78"/>
+      <c r="B13" s="81"/>
+      <c r="C13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="H13" s="88" t="s">
+      <c r="D13" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="42" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="91" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="28"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="26" t="s">
+      <c r="A14" s="78"/>
+      <c r="B14" s="82"/>
+      <c r="C14" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="F14" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="H14" s="88" t="s">
+      <c r="D14" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="42" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="45" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="17" t="s">
+      <c r="A15" s="78"/>
+      <c r="B15" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G15" s="9" t="s">
+      <c r="D15" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="105" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="12" t="s">
+      <c r="A16" s="78"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G16" s="13" t="s">
+      <c r="D16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="12" t="s">
+      <c r="A17" s="78"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G17" s="13" t="s">
+      <c r="D17" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="12" t="s">
+      <c r="A18" s="78"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G18" s="13" t="s">
+      <c r="D18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="12" t="s">
+      <c r="A19" s="78"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G19" s="13" t="s">
+      <c r="D19" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G19" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="46" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="28"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="26" t="s">
+      <c r="A20" s="78"/>
+      <c r="B20" s="74"/>
+      <c r="C20" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="F20" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="G20" s="27" t="s">
+      <c r="D20" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="15" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="28"/>
-      <c r="B21" s="17" t="s">
+      <c r="A21" s="78"/>
+      <c r="B21" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G21" s="9" t="s">
+      <c r="D21" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A22" s="28"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="12" t="s">
+      <c r="A22" s="78"/>
+      <c r="B22" s="73"/>
+      <c r="C22" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G22" s="13" t="s">
+      <c r="D22" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="45" x14ac:dyDescent="0.2">
-      <c r="A23" s="28"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="12" t="s">
+      <c r="A23" s="78"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G23" s="13" t="s">
+      <c r="D23" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G23" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A24" s="28"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="12" t="s">
+      <c r="A24" s="78"/>
+      <c r="B24" s="73"/>
+      <c r="C24" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G24" s="13" t="s">
+      <c r="D24" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="60" x14ac:dyDescent="0.2">
-      <c r="A25" s="28"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="12" t="s">
+      <c r="A25" s="78"/>
+      <c r="B25" s="73"/>
+      <c r="C25" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G25" s="13" t="s">
+      <c r="D25" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="61" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="28"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="15" t="s">
+      <c r="A26" s="78"/>
+      <c r="B26" s="84"/>
+      <c r="C26" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D26" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="F26" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="G26" s="16" t="s">
+      <c r="D26" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" s="9" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="46" x14ac:dyDescent="0.2">
-      <c r="A27" s="28"/>
-      <c r="B27" s="17" t="s">
+      <c r="A27" s="78"/>
+      <c r="B27" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D27" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G27" s="9" t="s">
+      <c r="D27" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="61" x14ac:dyDescent="0.2">
-      <c r="A28" s="28"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="21" t="s">
+      <c r="A28" s="78"/>
+      <c r="B28" s="73"/>
+      <c r="C28" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G28" s="13" t="s">
+      <c r="D28" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="61" x14ac:dyDescent="0.2">
-      <c r="A29" s="28"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="21" t="s">
+      <c r="A29" s="78"/>
+      <c r="B29" s="73"/>
+      <c r="C29" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G29" s="13" t="s">
+      <c r="D29" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G29" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="31" x14ac:dyDescent="0.2">
-      <c r="A30" s="28"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="21" t="s">
+      <c r="A30" s="78"/>
+      <c r="B30" s="73"/>
+      <c r="C30" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G30" s="13" t="s">
+      <c r="D30" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G30" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="61" x14ac:dyDescent="0.2">
-      <c r="A31" s="28"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="21" t="s">
+      <c r="A31" s="78"/>
+      <c r="B31" s="73"/>
+      <c r="C31" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G31" s="13" t="s">
+      <c r="D31" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G31" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="46" x14ac:dyDescent="0.2">
-      <c r="A32" s="28"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="21" t="s">
+      <c r="A32" s="78"/>
+      <c r="B32" s="73"/>
+      <c r="C32" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G32" s="13" t="s">
+      <c r="D32" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G32" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="46" x14ac:dyDescent="0.2">
-      <c r="A33" s="28"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="21" t="s">
+      <c r="A33" s="78"/>
+      <c r="B33" s="73"/>
+      <c r="C33" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G33" s="13" t="s">
+      <c r="D33" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G33" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="46" x14ac:dyDescent="0.2">
-      <c r="A34" s="28"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="21" t="s">
+      <c r="A34" s="78"/>
+      <c r="B34" s="73"/>
+      <c r="C34" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D34" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G34" s="13" t="s">
+      <c r="D34" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A35" s="28"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="12" t="s">
+      <c r="A35" s="78"/>
+      <c r="B35" s="73"/>
+      <c r="C35" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G35" s="13" t="s">
+      <c r="D35" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G35" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="60" x14ac:dyDescent="0.2">
-      <c r="A36" s="28"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="14" t="s">
+      <c r="A36" s="78"/>
+      <c r="B36" s="73"/>
+      <c r="C36" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G36" s="13" t="s">
+      <c r="D36" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="28"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="30" t="s">
+      <c r="A37" s="78"/>
+      <c r="B37" s="74"/>
+      <c r="C37" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D37" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="E37" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="F37" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="G37" s="27" t="s">
+      <c r="D37" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="G37" s="15" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="31" x14ac:dyDescent="0.2">
-      <c r="A38" s="28"/>
-      <c r="B38" s="31" t="s">
+      <c r="A38" s="78"/>
+      <c r="B38" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="C38" s="32" t="s">
+      <c r="C38" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D38" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="E38" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="F38" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="G38" s="33" t="s">
+      <c r="D38" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="G38" s="18" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="28"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="21" t="s">
+      <c r="A39" s="78"/>
+      <c r="B39" s="81"/>
+      <c r="C39" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="D39" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G39" s="13" t="s">
+      <c r="D39" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G39" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="31" x14ac:dyDescent="0.2">
-      <c r="A40" s="28"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="21" t="s">
+      <c r="A40" s="78"/>
+      <c r="B40" s="81"/>
+      <c r="C40" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D40" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F40" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G40" s="13" t="s">
+      <c r="D40" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="28"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="21" t="s">
+      <c r="A41" s="78"/>
+      <c r="B41" s="81"/>
+      <c r="C41" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D41" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G41" s="13" t="s">
+      <c r="D41" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G41" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="32" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="28"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="34" t="s">
+      <c r="A42" s="78"/>
+      <c r="B42" s="82"/>
+      <c r="C42" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="D42" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="E42" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="F42" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="G42" s="27" t="s">
+      <c r="D42" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F42" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="G42" s="15" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A43" s="28"/>
-      <c r="B43" s="35" t="s">
+      <c r="A43" s="78"/>
+      <c r="B43" s="86" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D43" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G43" s="9" t="s">
+      <c r="D43" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G43" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A44" s="28"/>
-      <c r="B44" s="36"/>
-      <c r="C44" s="12" t="s">
+      <c r="A44" s="78"/>
+      <c r="B44" s="87"/>
+      <c r="C44" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D44" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G44" s="13" t="s">
+      <c r="D44" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="45" x14ac:dyDescent="0.2">
-      <c r="A45" s="28"/>
-      <c r="B45" s="36"/>
-      <c r="C45" s="12" t="s">
+      <c r="A45" s="78"/>
+      <c r="B45" s="87"/>
+      <c r="C45" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D45" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G45" s="13" t="s">
+      <c r="D45" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G45" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="45" x14ac:dyDescent="0.2">
-      <c r="A46" s="28"/>
-      <c r="B46" s="36"/>
-      <c r="C46" s="12" t="s">
+      <c r="A46" s="78"/>
+      <c r="B46" s="87"/>
+      <c r="C46" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D46" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F46" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G46" s="13" t="s">
+      <c r="D46" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A47" s="28"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="23" t="s">
+      <c r="A47" s="78"/>
+      <c r="B47" s="87"/>
+      <c r="C47" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D47" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F47" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G47" s="13" t="s">
+      <c r="D47" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G47" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A48" s="28"/>
-      <c r="B48" s="36"/>
-      <c r="C48" s="12" t="s">
+      <c r="A48" s="78"/>
+      <c r="B48" s="87"/>
+      <c r="C48" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D48" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G48" s="13" t="s">
+      <c r="D48" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G48" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="28"/>
-      <c r="B49" s="36"/>
-      <c r="C49" s="15" t="s">
+      <c r="A49" s="78"/>
+      <c r="B49" s="87"/>
+      <c r="C49" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D49" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="E49" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="F49" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="G49" s="16" t="s">
+      <c r="D49" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G49" s="9" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A50" s="28"/>
-      <c r="B50" s="17" t="s">
+      <c r="A50" s="78"/>
+      <c r="B50" s="83" t="s">
         <v>52</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C50" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D50" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G50" s="9" t="s">
+      <c r="D50" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G50" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A51" s="28"/>
-      <c r="B51" s="18"/>
-      <c r="C51" s="12" t="s">
+      <c r="A51" s="78"/>
+      <c r="B51" s="73"/>
+      <c r="C51" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D51" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F51" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G51" s="13" t="s">
+      <c r="D51" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G51" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="31" x14ac:dyDescent="0.2">
-      <c r="A52" s="28"/>
-      <c r="B52" s="18"/>
-      <c r="C52" s="21" t="s">
+      <c r="A52" s="78"/>
+      <c r="B52" s="73"/>
+      <c r="C52" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D52" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F52" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G52" s="13" t="s">
+      <c r="D52" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="31" x14ac:dyDescent="0.2">
-      <c r="A53" s="28"/>
-      <c r="B53" s="18"/>
-      <c r="C53" s="21" t="s">
+      <c r="A53" s="78"/>
+      <c r="B53" s="73"/>
+      <c r="C53" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D53" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="E53" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="F53" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G53" s="13" t="s">
+      <c r="D53" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G53" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="31" x14ac:dyDescent="0.2">
-      <c r="A54" s="28"/>
-      <c r="B54" s="18"/>
-      <c r="C54" s="21" t="s">
+      <c r="A54" s="78"/>
+      <c r="B54" s="73"/>
+      <c r="C54" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D54" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="E54" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="F54" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G54" s="13" t="s">
+      <c r="D54" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="32" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="28"/>
-      <c r="B55" s="25"/>
-      <c r="C55" s="34" t="s">
+      <c r="A55" s="78"/>
+      <c r="B55" s="74"/>
+      <c r="C55" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="D55" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="E55" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="F55" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="G55" s="27" t="s">
+      <c r="D55" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="E55" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F55" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G55" s="15" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="31" x14ac:dyDescent="0.2">
-      <c r="A56" s="28"/>
-      <c r="B56" s="39" t="s">
+      <c r="A56" s="78"/>
+      <c r="B56" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="C56" s="32" t="s">
+      <c r="C56" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D56" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="E56" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="F56" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="G56" s="33" t="s">
+      <c r="D56" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E56" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F56" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="G56" s="18" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A57" s="28"/>
-      <c r="B57" s="18"/>
-      <c r="C57" s="12" t="s">
+      <c r="A57" s="78"/>
+      <c r="B57" s="73"/>
+      <c r="C57" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D57" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="E57" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="F57" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G57" s="13" t="s">
+      <c r="D57" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G57" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="105" x14ac:dyDescent="0.2">
-      <c r="A58" s="28"/>
-      <c r="B58" s="18"/>
-      <c r="C58" s="12" t="s">
+      <c r="A58" s="78"/>
+      <c r="B58" s="73"/>
+      <c r="C58" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D58" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="E58" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="F58" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G58" s="13" t="s">
+      <c r="D58" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G58" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="46" x14ac:dyDescent="0.2">
-      <c r="A59" s="28"/>
-      <c r="B59" s="18"/>
-      <c r="C59" s="21" t="s">
+      <c r="A59" s="78"/>
+      <c r="B59" s="73"/>
+      <c r="C59" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D59" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F59" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G59" s="13" t="s">
+      <c r="D59" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G59" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A60" s="28"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="12" t="s">
+      <c r="A60" s="78"/>
+      <c r="B60" s="73"/>
+      <c r="C60" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D60" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F60" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G60" s="13" t="s">
+      <c r="D60" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="75" x14ac:dyDescent="0.2">
-      <c r="A61" s="28"/>
-      <c r="B61" s="18"/>
-      <c r="C61" s="12" t="s">
+      <c r="A61" s="78"/>
+      <c r="B61" s="73"/>
+      <c r="C61" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D61" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E61" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F61" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G61" s="13" t="s">
+      <c r="D61" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G61" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="62" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="28"/>
-      <c r="B62" s="25"/>
-      <c r="C62" s="22" t="s">
+      <c r="A62" s="78"/>
+      <c r="B62" s="74"/>
+      <c r="C62" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D62" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="E62" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="F62" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="G62" s="16" t="s">
+      <c r="D62" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G62" s="9" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A63" s="28"/>
-      <c r="B63" s="41" t="s">
+      <c r="A63" s="78"/>
+      <c r="B63" s="75" t="s">
         <v>65</v>
       </c>
-      <c r="C63" s="42" t="s">
+      <c r="C63" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="D63" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E63" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G63" s="9" t="s">
+      <c r="D63" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G63" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A64" s="28"/>
-      <c r="B64" s="43"/>
-      <c r="C64" s="44" t="s">
+      <c r="A64" s="78"/>
+      <c r="B64" s="76"/>
+      <c r="C64" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="D64" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F64" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G64" s="13" t="s">
+      <c r="D64" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G64" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="45" x14ac:dyDescent="0.2">
-      <c r="A65" s="28"/>
-      <c r="B65" s="43"/>
-      <c r="C65" s="44" t="s">
+      <c r="A65" s="78"/>
+      <c r="B65" s="76"/>
+      <c r="C65" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="D65" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E65" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F65" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G65" s="13" t="s">
+      <c r="D65" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G65" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A66" s="28"/>
-      <c r="B66" s="43"/>
-      <c r="C66" s="44" t="s">
+      <c r="A66" s="78"/>
+      <c r="B66" s="76"/>
+      <c r="C66" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="D66" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E66" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F66" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G66" s="13" t="s">
+      <c r="D66" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G66" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A67" s="28"/>
-      <c r="B67" s="43"/>
-      <c r="C67" s="44" t="s">
+      <c r="A67" s="78"/>
+      <c r="B67" s="76"/>
+      <c r="C67" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="D67" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E67" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F67" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G67" s="13" t="s">
+      <c r="D67" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G67" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A68" s="28"/>
-      <c r="B68" s="43"/>
-      <c r="C68" s="44" t="s">
+      <c r="A68" s="78"/>
+      <c r="B68" s="76"/>
+      <c r="C68" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="D68" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E68" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F68" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G68" s="13" t="s">
+      <c r="D68" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A69" s="28"/>
-      <c r="B69" s="43"/>
-      <c r="C69" s="44" t="s">
+      <c r="A69" s="78"/>
+      <c r="B69" s="76"/>
+      <c r="C69" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="D69" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E69" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F69" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G69" s="13" t="s">
+      <c r="D69" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G69" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="45"/>
-      <c r="B70" s="46"/>
-      <c r="C70" s="47" t="s">
+      <c r="A70" s="79"/>
+      <c r="B70" s="77"/>
+      <c r="C70" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="D70" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="E70" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="F70" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="G70" s="27" t="s">
+      <c r="D70" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E70" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F70" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G70" s="15" t="s">
         <v>77</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C3"/>
     <mergeCell ref="B56:B62"/>
     <mergeCell ref="B63:B70"/>
     <mergeCell ref="A4:A70"/>
@@ -4082,11 +4207,8 @@
     <mergeCell ref="B38:B42"/>
     <mergeCell ref="B43:B49"/>
     <mergeCell ref="B50:B55"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D1:G70 H1 H4:H5 H7:H14">
+  <conditionalFormatting sqref="H1 D1:G70 H4:H5 H7:H14">
     <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
       <formula>"Not applicable"</formula>
     </cfRule>
@@ -4094,7 +4216,7 @@
       <formula>"Discontinue"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:G70 H4:H5 H7:H14">
+  <conditionalFormatting sqref="H4:H5 D4:G70 H7:H14">
     <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
       <formula>"Minimum"</formula>
     </cfRule>
@@ -4120,7 +4242,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="77.33203125" style="68" customWidth="1"/>
+    <col min="3" max="3" width="77.33203125" customWidth="1"/>
     <col min="4" max="4" width="17.6640625" customWidth="1"/>
     <col min="5" max="5" width="16.6640625" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
@@ -4128,1040 +4250,1040 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="95" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="99" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="54" t="s">
+      <c r="D2" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="G2" s="54" t="s">
+      <c r="G2" s="28" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3" t="str">
+      <c r="A3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="1" t="str">
         <f>'[1]Scenario overview'!B6</f>
         <v>A high-burden country close to reaching 95s across all populations</v>
       </c>
-      <c r="E3" s="3" t="str">
+      <c r="E3" s="1" t="str">
         <f>'[1]Scenario overview'!B7</f>
         <v>A high-burden country close to reaching 95s, but not in all populations</v>
       </c>
-      <c r="F3" s="3" t="str">
+      <c r="F3" s="1" t="str">
         <f>'[1]Scenario overview'!B8</f>
         <v>A high-burden country not yet achieving one or more of the 95s</v>
       </c>
-      <c r="G3" s="3" t="str">
+      <c r="G3" s="1" t="str">
         <f>'[1]Scenario overview'!B9</f>
         <v>A low-burden country achieving one or more of the 95s</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="55"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="57" t="str">
+      <c r="A4" s="98"/>
+      <c r="B4" s="100"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="29" t="str">
         <f>'[1]Scenario overview'!C6</f>
         <v>Limited, possibly some unsuppressed ART clients and some specific sub-segments that are generally underserved</v>
       </c>
-      <c r="E4" s="57" t="str">
+      <c r="E4" s="29" t="str">
         <f>'[1]Scenario overview'!C7</f>
         <v>Adolescent girls and young women, key populations, men</v>
       </c>
-      <c r="F4" s="57" t="str">
+      <c r="F4" s="29" t="str">
         <f>'[1]Scenario overview'!C8</f>
         <v>Clinically unstable/symptomatic, gaps in all population groups</v>
       </c>
-      <c r="G4" s="57" t="str">
+      <c r="G4" s="29" t="str">
         <f>'[1]Scenario overview'!C9</f>
         <v>Clinically unstable/symptomatic, gaps in all population groups</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="91" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="48" t="s">
+      <c r="B5" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="62" t="s">
+      <c r="C5" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="D5" s="58" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="58" t="s">
-        <v>75</v>
-      </c>
-      <c r="F5" s="58" t="s">
-        <v>75</v>
-      </c>
-      <c r="G5" s="58" t="s">
+      <c r="D5" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" s="30" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="10"/>
-      <c r="B6" s="17" t="s">
+      <c r="A6" s="92"/>
+      <c r="B6" s="83" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="63" t="s">
+      <c r="C6" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" s="9" t="s">
+      <c r="D6" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="10"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="64" t="s">
+      <c r="A7" s="92"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G7" s="13" t="s">
+      <c r="D7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="10"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="64" t="s">
+      <c r="A8" s="92"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G8" s="13" t="s">
+      <c r="D8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="10"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="64" t="s">
+      <c r="A9" s="92"/>
+      <c r="B9" s="81"/>
+      <c r="C9" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" s="13" t="s">
+      <c r="D9" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="64" t="s">
+      <c r="A10" s="92"/>
+      <c r="B10" s="81"/>
+      <c r="C10" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G10" s="13" t="s">
+      <c r="D10" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="64" t="s">
+      <c r="A11" s="92"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="13" t="s">
+      <c r="D11" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="64" t="s">
+      <c r="A12" s="92"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" s="13" t="s">
+      <c r="D12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="64" t="s">
+      <c r="A13" s="92"/>
+      <c r="B13" s="81"/>
+      <c r="C13" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D13" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="13" t="s">
+      <c r="D13" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="64" t="s">
+      <c r="A14" s="92"/>
+      <c r="B14" s="81"/>
+      <c r="C14" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" s="13" t="s">
+      <c r="D14" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="10"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="64" t="s">
+      <c r="A15" s="92"/>
+      <c r="B15" s="81"/>
+      <c r="C15" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G15" s="13" t="s">
+      <c r="D15" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="64" t="s">
+      <c r="A16" s="92"/>
+      <c r="B16" s="81"/>
+      <c r="C16" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G16" s="13" t="s">
+      <c r="D16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="64" t="s">
+      <c r="A17" s="92"/>
+      <c r="B17" s="81"/>
+      <c r="C17" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G17" s="13" t="s">
+      <c r="D17" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="64" t="s">
+      <c r="A18" s="92"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="13" t="s">
+      <c r="D18" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="64" t="s">
+      <c r="A19" s="92"/>
+      <c r="B19" s="81"/>
+      <c r="C19" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G19" s="13" t="s">
+      <c r="D19" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G19" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="10"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="64" t="s">
+      <c r="A20" s="92"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G20" s="13" t="s">
+      <c r="D20" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="10"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="64" t="s">
+      <c r="A21" s="92"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G21" s="13" t="s">
+      <c r="D21" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="10"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="64" t="s">
+      <c r="A22" s="92"/>
+      <c r="B22" s="81"/>
+      <c r="C22" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G22" s="13" t="s">
+      <c r="D22" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="10"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="64" t="s">
+      <c r="A23" s="92"/>
+      <c r="B23" s="81"/>
+      <c r="C23" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G23" s="13" t="s">
+      <c r="D23" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G23" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="10"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="64" t="s">
+      <c r="A24" s="92"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D24" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G24" s="13" t="s">
+      <c r="D24" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="10"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="64" t="s">
+      <c r="A25" s="92"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G25" s="13" t="s">
+      <c r="D25" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="10"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="64" t="s">
+      <c r="A26" s="92"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G26" s="13" t="s">
+      <c r="D26" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="65" t="s">
+      <c r="A27" s="92"/>
+      <c r="B27" s="82"/>
+      <c r="C27" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="D27" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="E27" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="F27" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="G27" s="27" t="s">
+      <c r="D27" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27" s="15" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="10"/>
-      <c r="B28" s="17" t="s">
+      <c r="A28" s="92"/>
+      <c r="B28" s="83" t="s">
         <v>91</v>
       </c>
-      <c r="C28" s="63" t="s">
+      <c r="C28" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D28" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G28" s="9" t="s">
+      <c r="D28" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="10"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="64" t="s">
+      <c r="A29" s="92"/>
+      <c r="B29" s="73"/>
+      <c r="C29" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G29" s="13" t="s">
+      <c r="D29" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="10"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="64" t="s">
+      <c r="A30" s="92"/>
+      <c r="B30" s="73"/>
+      <c r="C30" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G30" s="13" t="s">
+      <c r="D30" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="10"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="64" t="s">
+      <c r="A31" s="92"/>
+      <c r="B31" s="73"/>
+      <c r="C31" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G31" s="13" t="s">
+      <c r="D31" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G31" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="10"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="64" t="s">
+      <c r="A32" s="92"/>
+      <c r="B32" s="73"/>
+      <c r="C32" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="D32" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G32" s="13" t="s">
+      <c r="D32" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G32" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="10"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="64" t="s">
+      <c r="A33" s="92"/>
+      <c r="B33" s="73"/>
+      <c r="C33" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G33" s="13" t="s">
+      <c r="D33" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G33" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="10"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="64" t="s">
+      <c r="A34" s="92"/>
+      <c r="B34" s="73"/>
+      <c r="C34" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D34" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G34" s="13" t="s">
+      <c r="D34" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="10"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="64" t="s">
+      <c r="A35" s="92"/>
+      <c r="B35" s="73"/>
+      <c r="C35" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="D35" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G35" s="13" t="s">
+      <c r="D35" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G35" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="10"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="64" t="s">
+      <c r="A36" s="92"/>
+      <c r="B36" s="73"/>
+      <c r="C36" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="D36" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G36" s="13" t="s">
+      <c r="D36" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="10"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="64" t="s">
+      <c r="A37" s="92"/>
+      <c r="B37" s="73"/>
+      <c r="C37" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D37" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G37" s="13" t="s">
+      <c r="D37" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G37" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="10"/>
-      <c r="B38" s="18"/>
-      <c r="C38" s="64" t="s">
+      <c r="A38" s="92"/>
+      <c r="B38" s="73"/>
+      <c r="C38" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E38" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G38" s="13" t="s">
+      <c r="E38" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="10"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="64" t="s">
+      <c r="A39" s="92"/>
+      <c r="B39" s="73"/>
+      <c r="C39" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D39" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G39" s="13" t="s">
+      <c r="D39" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G39" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
-      <c r="B40" s="19"/>
-      <c r="C40" s="66" t="s">
+      <c r="A40" s="92"/>
+      <c r="B40" s="84"/>
+      <c r="C40" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="D40" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="E40" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="F40" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="G40" s="16" t="s">
+      <c r="D40" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G40" s="9" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="59"/>
-      <c r="B41" s="17" t="s">
+      <c r="A41" s="93"/>
+      <c r="B41" s="83" t="s">
         <v>92</v>
       </c>
-      <c r="C41" s="63" t="s">
+      <c r="C41" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D41" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="G41" s="9" t="s">
+      <c r="D41" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G41" s="4" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="59"/>
-      <c r="B42" s="18"/>
-      <c r="C42" s="64" t="s">
+      <c r="A42" s="93"/>
+      <c r="B42" s="73"/>
+      <c r="C42" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E42" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G42" s="13" t="s">
+      <c r="E42" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="59"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="64" t="s">
+      <c r="A43" s="93"/>
+      <c r="B43" s="73"/>
+      <c r="C43" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D43" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F43" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G43" s="13" t="s">
+      <c r="D43" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G43" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" s="59"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="64" t="s">
+      <c r="A44" s="93"/>
+      <c r="B44" s="73"/>
+      <c r="C44" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D44" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G44" s="13" t="s">
+      <c r="D44" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="59"/>
-      <c r="B45" s="18"/>
-      <c r="C45" s="64" t="s">
+      <c r="A45" s="93"/>
+      <c r="B45" s="73"/>
+      <c r="C45" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="D45" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G45" s="13" t="s">
+      <c r="D45" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G45" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" s="59"/>
-      <c r="B46" s="18"/>
-      <c r="C46" s="64" t="s">
+      <c r="A46" s="93"/>
+      <c r="B46" s="73"/>
+      <c r="C46" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="D46" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F46" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G46" s="13" t="s">
+      <c r="D46" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" s="59"/>
-      <c r="B47" s="18"/>
-      <c r="C47" s="64" t="s">
+      <c r="A47" s="93"/>
+      <c r="B47" s="73"/>
+      <c r="C47" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D47" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F47" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G47" s="13" t="s">
+      <c r="D47" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G47" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="59"/>
-      <c r="B48" s="18"/>
-      <c r="C48" s="64" t="s">
+      <c r="A48" s="93"/>
+      <c r="B48" s="73"/>
+      <c r="C48" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="D48" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G48" s="13" t="s">
+      <c r="D48" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G48" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49" s="59"/>
-      <c r="B49" s="18"/>
-      <c r="C49" s="64" t="s">
+      <c r="A49" s="93"/>
+      <c r="B49" s="73"/>
+      <c r="C49" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D49" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F49" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G49" s="13" t="s">
+      <c r="D49" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G49" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50" s="59"/>
-      <c r="B50" s="18"/>
-      <c r="C50" s="64" t="s">
+      <c r="A50" s="93"/>
+      <c r="B50" s="73"/>
+      <c r="C50" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="D50" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F50" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G50" s="13" t="s">
+      <c r="D50" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51" s="59"/>
-      <c r="B51" s="18"/>
-      <c r="C51" s="64" t="s">
+      <c r="A51" s="93"/>
+      <c r="B51" s="73"/>
+      <c r="C51" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="D51" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F51" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G51" s="13" t="s">
+      <c r="D51" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G51" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52" s="59"/>
-      <c r="B52" s="18"/>
-      <c r="C52" s="64" t="s">
+      <c r="A52" s="93"/>
+      <c r="B52" s="73"/>
+      <c r="C52" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="D52" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F52" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G52" s="13" t="s">
+      <c r="D52" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="59"/>
-      <c r="B53" s="25"/>
-      <c r="C53" s="67" t="s">
+      <c r="A53" s="93"/>
+      <c r="B53" s="74"/>
+      <c r="C53" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="D53" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="E53" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="F53" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="G53" s="27" t="s">
+      <c r="D53" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E53" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F53" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G53" s="15" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="24"/>
-      <c r="B54" s="49" t="s">
+      <c r="A54" s="94"/>
+      <c r="B54" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="C54" s="60" t="s">
+      <c r="C54" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="D54" s="61" t="s">
+      <c r="D54" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="E54" s="61" t="s">
+      <c r="E54" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="F54" s="61" t="s">
+      <c r="F54" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="G54" s="61" t="s">
+      <c r="G54" s="32" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5186,8 +5308,6 @@
     <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>"Optimal"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:G54">
     <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
       <formula>"Not applicable"</formula>
     </cfRule>
@@ -5211,7 +5331,7 @@
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
     <col min="2" max="2" width="23.1640625" customWidth="1"/>
-    <col min="3" max="3" width="54" style="68" customWidth="1"/>
+    <col min="3" max="3" width="54" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -5219,739 +5339,743 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="54" t="s">
+      <c r="A2" s="102"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="G2" s="54" t="s">
+      <c r="G2" s="28" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="72"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3" t="str">
+      <c r="A3" s="103"/>
+      <c r="B3" s="105"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="1" t="str">
         <f>'[1]Scenario overview'!B6</f>
         <v>A high-burden country close to reaching 95s across all populations</v>
       </c>
-      <c r="E3" s="3" t="str">
+      <c r="E3" s="1" t="str">
         <f>'[1]Scenario overview'!B7</f>
         <v>A high-burden country close to reaching 95s, but not in all populations</v>
       </c>
-      <c r="F3" s="3" t="str">
+      <c r="F3" s="1" t="str">
         <f>'[1]Scenario overview'!B8</f>
         <v>A high-burden country not yet achieving one or more of the 95s</v>
       </c>
-      <c r="G3" s="3" t="str">
+      <c r="G3" s="1" t="str">
         <f>'[1]Scenario overview'!B9</f>
         <v>A low-burden country achieving one or more of the 95s</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5" t="str">
+      <c r="A4" s="103"/>
+      <c r="B4" s="106"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="2" t="str">
         <f>'[1]Scenario overview'!C6</f>
         <v>Limited, possibly some unsuppressed ART clients and some specific sub-segments that are generally underserved</v>
       </c>
-      <c r="E4" s="5" t="str">
+      <c r="E4" s="2" t="str">
         <f>'[1]Scenario overview'!C7</f>
         <v>Adolescent girls and young women, key populations, men</v>
       </c>
-      <c r="F4" s="5" t="str">
+      <c r="F4" s="2" t="str">
         <f>'[1]Scenario overview'!C8</f>
         <v>Clinically unstable/symptomatic, gaps in all population groups</v>
       </c>
-      <c r="G4" s="5" t="str">
+      <c r="G4" s="2" t="str">
         <f>'[1]Scenario overview'!C9</f>
         <v>Clinically unstable/symptomatic, gaps in all population groups</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="78" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="C5" s="63" t="s">
+      <c r="C5" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G5" s="9" t="s">
+      <c r="D5" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="28"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="64" t="s">
+      <c r="A6" s="78"/>
+      <c r="B6" s="73"/>
+      <c r="C6" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" s="13" t="s">
+      <c r="D6" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="65" t="s">
+      <c r="A7" s="78"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="D7" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="G7" s="27" t="s">
+      <c r="D7" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="15" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="28"/>
-      <c r="B8" s="17" t="s">
+      <c r="A8" s="78"/>
+      <c r="B8" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="63" t="s">
+      <c r="C8" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G8" s="9" t="s">
+      <c r="D8" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="65" t="s">
+      <c r="A9" s="78"/>
+      <c r="B9" s="74"/>
+      <c r="C9" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="D9" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="F9" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" s="27" t="s">
+      <c r="D9" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" s="15" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="17" t="s">
+      <c r="A10" s="78"/>
+      <c r="B10" s="83" t="s">
         <v>97</v>
       </c>
-      <c r="C10" s="63" t="s">
+      <c r="C10" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G10" s="9" t="s">
+      <c r="D10" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="64" t="s">
+      <c r="A11" s="78"/>
+      <c r="B11" s="73"/>
+      <c r="C11" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="13" t="s">
+      <c r="D11" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="28"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="65" t="s">
+      <c r="A12" s="78"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="D12" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" s="27" t="s">
+      <c r="D12" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="15" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="17" t="s">
+      <c r="A13" s="78"/>
+      <c r="B13" s="83" t="s">
         <v>98</v>
       </c>
-      <c r="C13" s="63" t="s">
+      <c r="C13" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G13" s="9" t="s">
+      <c r="D13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="64" t="s">
+      <c r="A14" s="78"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" s="13" t="s">
+      <c r="D14" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="64" t="s">
+      <c r="A15" s="78"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G15" s="13" t="s">
+      <c r="D15" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="64" t="s">
+      <c r="A16" s="78"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G16" s="13" t="s">
+      <c r="D16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="64" t="s">
+      <c r="A17" s="78"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17" s="13" t="s">
+      <c r="D17" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="75" t="s">
+      <c r="A18" s="78"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="13" t="s">
+      <c r="D18" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="64" t="s">
+      <c r="A19" s="78"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="13" t="s">
+      <c r="D19" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="28"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="64" t="s">
+      <c r="A20" s="78"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G20" s="13" t="s">
+      <c r="D20" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="28"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="64" t="s">
+      <c r="A21" s="78"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G21" s="13" t="s">
+      <c r="D21" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="28"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="64" t="s">
+      <c r="A22" s="78"/>
+      <c r="B22" s="73"/>
+      <c r="C22" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G22" s="13" t="s">
+      <c r="D22" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="28"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="65" t="s">
+      <c r="A23" s="78"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="D23" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="E23" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="F23" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="G23" s="27" t="s">
+      <c r="D23" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" s="15" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="28"/>
-      <c r="B24" s="17" t="s">
+      <c r="A24" s="78"/>
+      <c r="B24" s="83" t="s">
         <v>99</v>
       </c>
-      <c r="C24" s="63" t="s">
+      <c r="C24" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G24" s="9" t="s">
+      <c r="D24" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="28"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="64" t="s">
+      <c r="A25" s="78"/>
+      <c r="B25" s="73"/>
+      <c r="C25" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G25" s="13" t="s">
+      <c r="D25" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="28"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="64" t="s">
+      <c r="A26" s="78"/>
+      <c r="B26" s="73"/>
+      <c r="C26" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G26" s="13" t="s">
+      <c r="D26" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="28"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="64" t="s">
+      <c r="A27" s="78"/>
+      <c r="B27" s="73"/>
+      <c r="C27" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G27" s="13" t="s">
+      <c r="D27" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="28"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="64" t="s">
+      <c r="A28" s="78"/>
+      <c r="B28" s="73"/>
+      <c r="C28" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G28" s="13" t="s">
+      <c r="D28" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="28"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="64" t="s">
+      <c r="A29" s="78"/>
+      <c r="B29" s="73"/>
+      <c r="C29" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G29" s="13" t="s">
+      <c r="D29" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="28"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="64" t="s">
+      <c r="A30" s="78"/>
+      <c r="B30" s="73"/>
+      <c r="C30" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G30" s="13" t="s">
+      <c r="D30" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="28"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="64" t="s">
+      <c r="A31" s="78"/>
+      <c r="B31" s="73"/>
+      <c r="C31" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G31" s="13" t="s">
+      <c r="D31" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G31" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="28"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="64" t="s">
+      <c r="A32" s="78"/>
+      <c r="B32" s="73"/>
+      <c r="C32" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="D32" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G32" s="13" t="s">
+      <c r="D32" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G32" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="28"/>
-      <c r="B33" s="25"/>
-      <c r="C33" s="65" t="s">
+      <c r="A33" s="78"/>
+      <c r="B33" s="74"/>
+      <c r="C33" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="D33" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="E33" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="F33" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="G33" s="27" t="s">
+      <c r="D33" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="G33" s="15" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="28"/>
-      <c r="B34" s="17" t="s">
+      <c r="A34" s="78"/>
+      <c r="B34" s="83" t="s">
         <v>100</v>
       </c>
-      <c r="C34" s="76" t="s">
+      <c r="C34" s="35" t="s">
         <v>182</v>
       </c>
-      <c r="D34" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G34" s="9" t="s">
+      <c r="D34" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="28"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="77" t="s">
+      <c r="A35" s="78"/>
+      <c r="B35" s="73"/>
+      <c r="C35" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="D35" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G35" s="13" t="s">
+      <c r="D35" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G35" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="28"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="64" t="s">
+      <c r="A36" s="78"/>
+      <c r="B36" s="73"/>
+      <c r="C36" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D36" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G36" s="13" t="s">
+      <c r="D36" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="28"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="65" t="s">
+      <c r="A37" s="78"/>
+      <c r="B37" s="74"/>
+      <c r="C37" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="D37" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="E37" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="F37" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="G37" s="27" t="s">
+      <c r="D37" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G37" s="15" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="45"/>
-      <c r="B38" s="48" t="s">
+      <c r="A38" s="79"/>
+      <c r="B38" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C38" s="62" t="s">
+      <c r="C38" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="D38" s="58" t="s">
-        <v>77</v>
-      </c>
-      <c r="E38" s="58" t="s">
-        <v>77</v>
-      </c>
-      <c r="F38" s="58" t="s">
-        <v>76</v>
-      </c>
-      <c r="G38" s="58" t="s">
+      <c r="D38" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="E38" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="F38" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="G38" s="30" t="s">
         <v>77</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
     <mergeCell ref="A5:A38"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B9"/>
@@ -5959,28 +6083,22 @@
     <mergeCell ref="B13:B23"/>
     <mergeCell ref="B24:B33"/>
     <mergeCell ref="B34:B37"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:G38">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"Not applicable"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"Discontinue"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"Minimum"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"Standard"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"Optimal"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:G38">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>"Not applicable"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>"Discontinue"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -5994,7 +6112,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{572C777E-CA3B-2741-A6EF-7E74D6D879C4}">
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
@@ -6007,636 +6125,766 @@
     <col min="10" max="10" width="64.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" s="67" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80" t="s">
+      <c r="B3" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="80" t="s">
+      <c r="C3" s="111" t="s">
         <v>197</v>
       </c>
-      <c r="D1" s="80" t="s">
+      <c r="D3" s="111" t="s">
         <v>198</v>
       </c>
-      <c r="E1" s="80" t="s">
+      <c r="E3" s="111" t="s">
         <v>204</v>
       </c>
-      <c r="F1" s="80" t="s">
+      <c r="F3" s="111" t="s">
         <v>201</v>
       </c>
-      <c r="G1" s="80" t="s">
+      <c r="G3" s="111" t="s">
         <v>200</v>
       </c>
-      <c r="H1" s="80" t="s">
+      <c r="H3" s="112" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="82" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="113" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="89" t="s">
+      <c r="B4" s="43" t="s">
         <v>194</v>
       </c>
-      <c r="C2" s="100" t="s">
+      <c r="C4" s="55" t="s">
         <v>202</v>
       </c>
-      <c r="D2" s="100" t="s">
+      <c r="D4" s="55" t="s">
         <v>202</v>
       </c>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100" t="s">
+      <c r="E4" s="55"/>
+      <c r="F4" s="55" t="s">
         <v>202</v>
       </c>
-      <c r="G2" s="100" t="s">
+      <c r="G4" s="55" t="s">
         <v>202</v>
       </c>
-      <c r="H2" s="101" t="s">
+      <c r="H4" s="56" t="s">
         <v>202</v>
       </c>
-      <c r="J2" s="97" t="s">
+      <c r="J4" s="53" t="s">
         <v>206</v>
       </c>
-      <c r="K2" s="98"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="82"/>
-      <c r="B3" s="102" t="s">
+      <c r="K4" s="54"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="113"/>
+      <c r="B5" s="57" t="s">
         <v>193</v>
       </c>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="103"/>
-      <c r="J3" t="s">
+      <c r="C5" s="114"/>
+      <c r="D5" s="114"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="58"/>
+      <c r="J5" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="82"/>
-      <c r="B4" s="102" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="113"/>
+      <c r="B6" s="57" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="93"/>
-      <c r="J4" s="96"/>
-    </row>
-    <row r="5" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="82"/>
-      <c r="B5" s="104" t="s">
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
+      <c r="F6" s="108"/>
+      <c r="G6" s="108"/>
+      <c r="H6" s="49"/>
+      <c r="J6" s="52"/>
+    </row>
+    <row r="7" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="113"/>
+      <c r="B7" s="59" t="s">
         <v>191</v>
       </c>
-      <c r="C5" s="94"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="95"/>
-      <c r="J5" s="96"/>
-    </row>
-    <row r="6" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="83"/>
-      <c r="B6" s="105" t="s">
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="51"/>
+      <c r="J7" s="52"/>
+    </row>
+    <row r="8" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="115"/>
+      <c r="B8" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="106"/>
-      <c r="D6" s="106"/>
-      <c r="E6" s="106"/>
-      <c r="F6" s="106"/>
-      <c r="G6" s="106"/>
-      <c r="H6" s="109" t="s">
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="64" t="s">
         <v>202</v>
       </c>
-      <c r="J6" t="s">
+    </row>
+    <row r="9" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="115"/>
+      <c r="B9" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>202</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>202</v>
+      </c>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55" t="s">
+        <v>202</v>
+      </c>
+      <c r="G9" s="55" t="s">
+        <v>202</v>
+      </c>
+      <c r="H9" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="J9" s="66"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="115"/>
+      <c r="B10" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="65" t="s">
+        <v>202</v>
+      </c>
+      <c r="H10" s="48"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" s="115"/>
+      <c r="B11" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="108"/>
+      <c r="D11" s="108"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="49"/>
+      <c r="J11" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" s="115"/>
+      <c r="B12" s="62" t="s">
+        <v>196</v>
+      </c>
+      <c r="C12" s="108"/>
+      <c r="D12" s="108"/>
+      <c r="E12" s="108"/>
+      <c r="F12" s="108"/>
+      <c r="G12" s="108"/>
+      <c r="H12" s="49"/>
+    </row>
+    <row r="13" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="115"/>
+      <c r="B13" s="63" t="s">
+        <v>203</v>
+      </c>
+      <c r="C13" s="50"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="51"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" s="115"/>
+      <c r="B14" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="J14" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="83"/>
-      <c r="B7" s="105" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="100" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="115"/>
+      <c r="B15" s="62" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="108"/>
+      <c r="D15" s="108"/>
+      <c r="E15" s="108"/>
+      <c r="F15" s="108"/>
+      <c r="G15" s="108"/>
+      <c r="H15" s="49"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="115"/>
+      <c r="B16" s="62" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="108"/>
+      <c r="D16" s="108"/>
+      <c r="E16" s="108"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="49"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="115"/>
+      <c r="B17" s="62" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="108"/>
+      <c r="D17" s="108"/>
+      <c r="E17" s="108"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="108"/>
+      <c r="H17" s="49"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="115"/>
+      <c r="B18" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="108"/>
+      <c r="D18" s="108"/>
+      <c r="E18" s="108"/>
+      <c r="F18" s="108"/>
+      <c r="G18" s="108"/>
+      <c r="H18" s="49"/>
+      <c r="J18" s="67"/>
+    </row>
+    <row r="19" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="115"/>
+      <c r="B19" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="51"/>
+      <c r="J19" s="68"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="115"/>
+      <c r="B20" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="44" t="s">
         <v>202</v>
       </c>
-      <c r="D7" s="100" t="s">
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="115"/>
+      <c r="B21" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="108"/>
+      <c r="D21" s="108"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="108"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="49"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" s="115"/>
+      <c r="B22" s="62" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="108"/>
+      <c r="D22" s="108"/>
+      <c r="E22" s="108"/>
+      <c r="F22" s="108"/>
+      <c r="G22" s="108"/>
+      <c r="H22" s="49"/>
+      <c r="J22" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="115"/>
+      <c r="B23" s="62" t="s">
+        <v>215</v>
+      </c>
+      <c r="C23" s="108"/>
+      <c r="D23" s="108"/>
+      <c r="E23" s="108"/>
+      <c r="F23" s="108"/>
+      <c r="G23" s="108"/>
+      <c r="H23" s="49"/>
+    </row>
+    <row r="24" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="115"/>
+      <c r="B24" s="63" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="51"/>
+      <c r="J24" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="115"/>
+      <c r="B25" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="44" t="s">
         <v>202</v>
       </c>
-      <c r="E7" s="100"/>
-      <c r="F7" s="100" t="s">
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="115"/>
+      <c r="B26" s="62" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="108"/>
+      <c r="D26" s="108"/>
+      <c r="E26" s="108"/>
+      <c r="F26" s="108"/>
+      <c r="G26" s="108"/>
+      <c r="H26" s="49"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="115"/>
+      <c r="B27" s="62" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="108"/>
+      <c r="D27" s="108"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="108"/>
+      <c r="G27" s="108"/>
+      <c r="H27" s="49"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="115"/>
+      <c r="B28" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="108"/>
+      <c r="D28" s="108"/>
+      <c r="E28" s="108"/>
+      <c r="F28" s="108"/>
+      <c r="G28" s="108"/>
+      <c r="H28" s="49"/>
+    </row>
+    <row r="29" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="115"/>
+      <c r="B29" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="108"/>
+      <c r="D29" s="108"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="108"/>
+      <c r="G29" s="108"/>
+      <c r="H29" s="49"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="115"/>
+      <c r="B30" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="65" t="s">
         <v>202</v>
       </c>
-      <c r="G7" s="100" t="s">
+      <c r="G30" s="65" t="s">
         <v>202</v>
       </c>
-      <c r="H7" s="101" t="s">
+      <c r="H30" s="44" t="s">
         <v>202</v>
       </c>
-      <c r="J7" s="115" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="83"/>
-      <c r="B8" s="89" t="s">
+      <c r="J30" s="39"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" s="115"/>
+      <c r="B31" s="62" t="s">
+        <v>211</v>
+      </c>
+      <c r="C31" s="107"/>
+      <c r="D31" s="107"/>
+      <c r="E31" s="108"/>
+      <c r="F31" s="109"/>
+      <c r="G31" s="109"/>
+      <c r="H31" s="45"/>
+      <c r="J31" s="39"/>
+    </row>
+    <row r="32" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="115"/>
+      <c r="B32" s="63" t="s">
+        <v>212</v>
+      </c>
+      <c r="C32" s="69"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="46"/>
+      <c r="J32" s="39" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="115"/>
+      <c r="B33" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="65" t="s">
+        <v>202</v>
+      </c>
+      <c r="G33" s="65" t="s">
+        <v>202</v>
+      </c>
+      <c r="H33" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="J33" s="39"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" s="115"/>
+      <c r="B34" s="62" t="s">
+        <v>217</v>
+      </c>
+      <c r="C34" s="107"/>
+      <c r="D34" s="107"/>
+      <c r="E34" s="108"/>
+      <c r="F34" s="109"/>
+      <c r="G34" s="109"/>
+      <c r="H34" s="45"/>
+      <c r="J34" s="39"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" s="115"/>
+      <c r="B35" s="62" t="s">
+        <v>218</v>
+      </c>
+      <c r="C35" s="107"/>
+      <c r="D35" s="107"/>
+      <c r="E35" s="108"/>
+      <c r="F35" s="109"/>
+      <c r="G35" s="109"/>
+      <c r="H35" s="45"/>
+      <c r="J35" s="39"/>
+    </row>
+    <row r="36" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="116"/>
+      <c r="B36" s="63" t="s">
+        <v>219</v>
+      </c>
+      <c r="C36" s="50"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="46"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" s="127" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" s="118" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="119"/>
+      <c r="D37" s="119"/>
+      <c r="E37" s="118" t="s">
+        <v>202</v>
+      </c>
+      <c r="F37" s="119"/>
+      <c r="G37" s="119"/>
+      <c r="H37" s="120"/>
+      <c r="J37" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" s="128"/>
+      <c r="B38" s="121" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="122"/>
+      <c r="D38" s="122"/>
+      <c r="E38" s="121" t="s">
+        <v>202</v>
+      </c>
+      <c r="F38" s="122"/>
+      <c r="G38" s="122"/>
+      <c r="H38" s="123"/>
+      <c r="J38" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" s="128"/>
+      <c r="B39" s="121" t="s">
+        <v>225</v>
+      </c>
+      <c r="C39" s="122"/>
+      <c r="D39" s="122"/>
+      <c r="E39" s="121" t="s">
+        <v>202</v>
+      </c>
+      <c r="F39" s="122"/>
+      <c r="G39" s="122"/>
+      <c r="H39" s="123"/>
+    </row>
+    <row r="40" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="129"/>
+      <c r="B40" s="124" t="s">
+        <v>222</v>
+      </c>
+      <c r="C40" s="125"/>
+      <c r="D40" s="125"/>
+      <c r="E40" s="124" t="s">
+        <v>202</v>
+      </c>
+      <c r="F40" s="125"/>
+      <c r="G40" s="125"/>
+      <c r="H40" s="126"/>
+    </row>
+    <row r="41" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A41" s="143" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="C41" s="41"/>
+      <c r="D41" s="141" t="s">
+        <v>202</v>
+      </c>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="41"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" s="144"/>
+      <c r="B42" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C42" s="40" t="s">
+        <v>202</v>
+      </c>
+      <c r="D42" s="41"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="41"/>
+      <c r="G42" s="41"/>
+      <c r="H42" s="41"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A43" s="144"/>
+      <c r="B43" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="40" t="s">
+        <v>202</v>
+      </c>
+      <c r="D43" s="41"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="41"/>
+      <c r="G43" s="41"/>
+      <c r="H43" s="41"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A44" s="144"/>
+      <c r="B44" s="40" t="s">
+        <v>227</v>
+      </c>
+      <c r="C44" s="40" t="s">
+        <v>202</v>
+      </c>
+      <c r="D44" s="41"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="41"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="41"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A45" s="144"/>
+      <c r="B45" s="142" t="s">
+        <v>228</v>
+      </c>
+      <c r="C45" s="40"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="41"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="41"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A46" s="144"/>
+      <c r="B46" s="142" t="s">
+        <v>229</v>
+      </c>
+      <c r="C46" s="40"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="41"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="41"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A47" s="144"/>
+      <c r="B47" s="142" t="s">
+        <v>230</v>
+      </c>
+      <c r="C47" s="40"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="41"/>
+      <c r="G47" s="41"/>
+      <c r="H47" s="41"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A48" s="144"/>
+      <c r="B48" s="40" t="s">
+        <v>231</v>
+      </c>
+      <c r="C48" s="40" t="s">
+        <v>202</v>
+      </c>
+      <c r="D48" s="41"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="41"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="41"/>
+    </row>
+    <row r="49" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="145"/>
+      <c r="B49" s="40" t="s">
+        <v>234</v>
+      </c>
+      <c r="C49" s="40" t="s">
+        <v>202</v>
+      </c>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="41"/>
+      <c r="J49" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A50" s="138" t="s">
+        <v>205</v>
+      </c>
+      <c r="B50" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="91"/>
-      <c r="D8" s="91"/>
-      <c r="E8" s="91"/>
-      <c r="F8" s="91"/>
-      <c r="G8" s="111" t="s">
-        <v>202</v>
-      </c>
-      <c r="H8" s="92"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="83"/>
-      <c r="B9" s="107" t="s">
-        <v>195</v>
-      </c>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="93"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="83"/>
-      <c r="B10" s="107" t="s">
-        <v>196</v>
-      </c>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="93"/>
-    </row>
-    <row r="11" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="83"/>
-      <c r="B11" s="108" t="s">
-        <v>203</v>
-      </c>
-      <c r="C11" s="94"/>
-      <c r="D11" s="94"/>
-      <c r="E11" s="94"/>
-      <c r="F11" s="94"/>
-      <c r="G11" s="94"/>
-      <c r="H11" s="95"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="83"/>
-      <c r="B12" s="89" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="91"/>
-      <c r="D12" s="91"/>
-      <c r="E12" s="91"/>
-      <c r="F12" s="91"/>
-      <c r="G12" s="91"/>
-      <c r="H12" s="90" t="s">
-        <v>202</v>
-      </c>
-      <c r="J12" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="83"/>
-      <c r="B13" s="107" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="93"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="83"/>
-      <c r="B14" s="107" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="83"/>
-      <c r="D14" s="83"/>
-      <c r="E14" s="83"/>
-      <c r="F14" s="83"/>
-      <c r="G14" s="83"/>
-      <c r="H14" s="93"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="83"/>
-      <c r="B15" s="107" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="83"/>
-      <c r="H15" s="93"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="83"/>
-      <c r="B16" s="107" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="83"/>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="83"/>
-      <c r="H16" s="93"/>
-    </row>
-    <row r="17" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="83"/>
-      <c r="B17" s="108" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="94"/>
-      <c r="D17" s="94"/>
-      <c r="E17" s="94"/>
-      <c r="F17" s="94"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="95"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="83"/>
-      <c r="B18" s="89" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="91"/>
-      <c r="D18" s="91"/>
-      <c r="E18" s="91"/>
-      <c r="F18" s="91"/>
-      <c r="G18" s="91"/>
-      <c r="H18" s="90" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="83"/>
-      <c r="B19" s="107" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="83"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="83"/>
-      <c r="G19" s="83"/>
-      <c r="H19" s="93"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="83"/>
-      <c r="B20" s="107" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="83"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="83"/>
-      <c r="G20" s="83"/>
-      <c r="H20" s="93"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="83"/>
-      <c r="B21" s="107" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="83"/>
-      <c r="D21" s="83"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="83"/>
-      <c r="G21" s="83"/>
-      <c r="H21" s="93"/>
-    </row>
-    <row r="22" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="83"/>
-      <c r="B22" s="108" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="94"/>
-      <c r="D22" s="94"/>
-      <c r="E22" s="94"/>
-      <c r="F22" s="94"/>
-      <c r="G22" s="94"/>
-      <c r="H22" s="95"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="83"/>
-      <c r="B23" s="89" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="91"/>
-      <c r="D23" s="91"/>
-      <c r="E23" s="91"/>
-      <c r="F23" s="91"/>
-      <c r="G23" s="91"/>
-      <c r="H23" s="90" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="83"/>
-      <c r="B24" s="107" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="83"/>
-      <c r="D24" s="83"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="93"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="83"/>
-      <c r="B25" s="107" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="83"/>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="83"/>
-      <c r="H25" s="93"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="83"/>
-      <c r="B26" s="107" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="83"/>
-      <c r="D26" s="83"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="83"/>
-      <c r="G26" s="83"/>
-      <c r="H26" s="93"/>
-    </row>
-    <row r="27" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="83"/>
-      <c r="B27" s="108" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="94"/>
-      <c r="D27" s="94"/>
-      <c r="E27" s="94"/>
-      <c r="F27" s="94"/>
-      <c r="G27" s="94"/>
-      <c r="H27" s="95"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="83"/>
-      <c r="B28" s="82" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="100" t="s">
-        <v>202</v>
-      </c>
-      <c r="D28" s="100" t="s">
-        <v>202</v>
-      </c>
-      <c r="E28" s="83"/>
-      <c r="F28" s="82" t="s">
-        <v>202</v>
-      </c>
-      <c r="G28" s="82" t="s">
-        <v>202</v>
-      </c>
-      <c r="H28" s="82" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="83"/>
-      <c r="B29" s="82" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="83"/>
-      <c r="D29" s="83"/>
-      <c r="E29" s="83"/>
-      <c r="F29" s="83"/>
-      <c r="G29" s="83"/>
-      <c r="H29" s="83"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="84" t="s">
-        <v>88</v>
-      </c>
-      <c r="B30" s="84" t="s">
-        <v>89</v>
-      </c>
-      <c r="C30" s="81"/>
-      <c r="D30" s="81"/>
-      <c r="E30" s="81"/>
-      <c r="F30" s="81"/>
-      <c r="G30" s="81"/>
-      <c r="H30" s="81"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="85"/>
-      <c r="B31" s="84" t="s">
-        <v>90</v>
-      </c>
-      <c r="C31" s="81"/>
-      <c r="D31" s="81"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="81"/>
-      <c r="G31" s="81"/>
-      <c r="H31" s="81"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="85"/>
-      <c r="B32" s="84" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" s="81"/>
-      <c r="D32" s="81"/>
-      <c r="E32" s="81"/>
-      <c r="F32" s="81"/>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="85"/>
-      <c r="B33" s="84" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33" s="81"/>
-      <c r="D33" s="81"/>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="81"/>
-      <c r="H33" s="81"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="85"/>
-      <c r="B34" s="84" t="s">
-        <v>93</v>
-      </c>
-      <c r="C34" s="81"/>
-      <c r="D34" s="81"/>
-      <c r="E34" s="81"/>
-      <c r="F34" s="81"/>
-      <c r="G34" s="81"/>
-      <c r="H34" s="81"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="86" t="s">
-        <v>94</v>
-      </c>
-      <c r="B35" s="86" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" s="81"/>
-      <c r="D35" s="110"/>
-      <c r="E35" s="81"/>
-      <c r="F35" s="81"/>
-      <c r="G35" s="81"/>
-      <c r="H35" s="81"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="87"/>
-      <c r="B36" s="86" t="s">
-        <v>96</v>
-      </c>
-      <c r="C36" s="81"/>
-      <c r="D36" s="81"/>
-      <c r="E36" s="81"/>
-      <c r="F36" s="81"/>
-      <c r="G36" s="81"/>
-      <c r="H36" s="81"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="87"/>
-      <c r="B37" s="86" t="s">
-        <v>97</v>
-      </c>
-      <c r="C37" s="81"/>
-      <c r="D37" s="81"/>
-      <c r="E37" s="81"/>
-      <c r="F37" s="81"/>
-      <c r="G37" s="81"/>
-      <c r="H37" s="81"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="87"/>
-      <c r="B38" s="86" t="s">
-        <v>98</v>
-      </c>
-      <c r="C38" s="81"/>
-      <c r="D38" s="81"/>
-      <c r="E38" s="81"/>
-      <c r="F38" s="81"/>
-      <c r="G38" s="81"/>
-      <c r="H38" s="81"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="87"/>
-      <c r="B39" s="86" t="s">
-        <v>99</v>
-      </c>
-      <c r="C39" s="81"/>
-      <c r="D39" s="81"/>
-      <c r="E39" s="81"/>
-      <c r="F39" s="81"/>
-      <c r="G39" s="81"/>
-      <c r="H39" s="81"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="87"/>
-      <c r="B40" s="86" t="s">
-        <v>100</v>
-      </c>
-      <c r="C40" s="81"/>
-      <c r="D40" s="81"/>
-      <c r="E40" s="81"/>
-      <c r="F40" s="81"/>
-      <c r="G40" s="81"/>
-      <c r="H40" s="81"/>
-    </row>
-    <row r="41" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="87"/>
-      <c r="B41" s="86" t="s">
-        <v>101</v>
-      </c>
-      <c r="C41" s="81"/>
-      <c r="D41" s="81"/>
-      <c r="E41" s="81"/>
-      <c r="F41" s="81"/>
-      <c r="G41" s="81"/>
-      <c r="H41" s="81"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="112" t="s">
-        <v>205</v>
-      </c>
-      <c r="B42" s="113" t="s">
-        <v>26</v>
-      </c>
-      <c r="C42" s="114"/>
-      <c r="D42" s="114"/>
-      <c r="E42" s="114"/>
-      <c r="F42" s="114"/>
-      <c r="G42" s="114"/>
-      <c r="H42" s="114"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="81"/>
-      <c r="B43" s="81"/>
-      <c r="C43" s="81"/>
-      <c r="D43" s="81"/>
-      <c r="E43" s="81"/>
-      <c r="F43" s="81"/>
-      <c r="G43" s="81"/>
-      <c r="H43" s="81"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="81"/>
-      <c r="B44" s="81"/>
-      <c r="C44" s="81"/>
-      <c r="D44" s="81"/>
-      <c r="E44" s="81"/>
-      <c r="F44" s="81"/>
-      <c r="G44" s="81"/>
-      <c r="H44" s="81"/>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B51" s="32"/>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B52" s="21"/>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B53" s="21"/>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B54" s="21"/>
-    </row>
-    <row r="55" spans="2:2" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="34"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A67" s="32"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A68" s="21"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A69" s="21"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A70" s="21"/>
+      <c r="C50" s="130"/>
+      <c r="D50" s="130"/>
+      <c r="E50" s="130"/>
+      <c r="F50" s="130"/>
+      <c r="G50" s="130"/>
+      <c r="H50" s="131"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A51" s="139"/>
+      <c r="B51" s="117" t="s">
+        <v>220</v>
+      </c>
+      <c r="C51" s="132"/>
+      <c r="D51" s="132"/>
+      <c r="E51" s="132"/>
+      <c r="F51" s="132"/>
+      <c r="G51" s="132"/>
+      <c r="H51" s="133"/>
+      <c r="J51" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="140"/>
+      <c r="B52" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="C52" s="135"/>
+      <c r="D52" s="135"/>
+      <c r="E52" s="135"/>
+      <c r="F52" s="135"/>
+      <c r="G52" s="135"/>
+      <c r="H52" s="136"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B59" s="17"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B60" s="11"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B61" s="11"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B62" s="11"/>
+    </row>
+    <row r="63" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="19"/>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A75" s="17"/>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A76" s="11"/>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A77" s="11"/>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A78" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/TIER/Tier Summary.xlsx
+++ b/resources/TIER/Tier Summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29704"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/resources/TIER/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="8_{7FED5F5D-50A6-F84C-81AE-1EC42B6C714A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE8A48D5-0A59-416C-9F21-BD9FAA0EC666}"/>
+  <xr:revisionPtr revIDLastSave="150" documentId="8_{7FED5F5D-50A6-F84C-81AE-1EC42B6C714A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FF64FE1-9AEF-4BA5-AA39-FC9E3C71DCDA}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="1500" windowWidth="27240" windowHeight="15020" firstSheet="3" activeTab="3" xr2:uid="{F61A66A6-2BB4-B445-8D7A-81B0E2BBFC2C}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="244">
   <si>
     <t>HIV programme area</t>
   </si>
@@ -1360,6 +1360,9 @@
     <t>Impact will differ based on prevalence</t>
   </si>
   <si>
+    <t>Covered in the AHD package</t>
+  </si>
+  <si>
     <t>I'm not quite sure the best way to handle the lab tests</t>
   </si>
   <si>
@@ -1405,12 +1408,15 @@
     <t>This one might be hard to parameterize on short timelines</t>
   </si>
   <si>
-    <t>HIVST</t>
+    <t>HIVST (Facility-based)</t>
   </si>
   <si>
     <t>Maybe facility-based or community-based</t>
   </si>
   <si>
+    <t>HIVST (community-based)</t>
+  </si>
+  <si>
     <t>PEP (facility based, GBV and KP services)</t>
   </si>
   <si>
@@ -1430,6 +1436,9 @@
   </si>
   <si>
     <t>Harm reduction for people who inject drugs (facility based or existing KP services)</t>
+  </si>
+  <si>
+    <t>I think maybe not relevant enough for a general model...</t>
   </si>
   <si>
     <t>VMMC (esp. areas with high HIV prev and low circumcision prev)</t>
@@ -1454,7 +1463,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1536,7 +1545,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -1544,8 +1559,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <strike/>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
@@ -2077,7 +2110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2236,6 +2269,8 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2341,9 +2376,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2866,13 +2908,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="112" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="113" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="111" t="s">
+      <c r="C1" s="113" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -2892,9 +2934,9 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="110"/>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
       <c r="D2" s="1" t="str">
         <f>'[1]Scenario overview'!B6</f>
         <v>A high-burden country close to reaching 95s across all populations</v>
@@ -2916,9 +2958,9 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="17.100000000000001" thickBot="1">
-      <c r="A3" s="110"/>
-      <c r="B3" s="112"/>
-      <c r="C3" s="112"/>
+      <c r="A3" s="112"/>
+      <c r="B3" s="114"/>
+      <c r="C3" s="114"/>
       <c r="D3" s="2" t="str">
         <f>'[1]Scenario overview'!C6</f>
         <v>Limited, possibly some unsuppressed ART clients and some specific sub-segments that are generally underserved</v>
@@ -2937,10 +2979,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="45">
-      <c r="A4" s="119" t="s">
+      <c r="A4" s="121" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="121" t="s">
+      <c r="B4" s="123" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -2963,8 +3005,8 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="75">
-      <c r="A5" s="119"/>
-      <c r="B5" s="122"/>
+      <c r="A5" s="121"/>
+      <c r="B5" s="124"/>
       <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
@@ -2985,8 +3027,8 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="60">
-      <c r="A6" s="119"/>
-      <c r="B6" s="122"/>
+      <c r="A6" s="121"/>
+      <c r="B6" s="124"/>
       <c r="C6" s="5" t="s">
         <v>16</v>
       </c>
@@ -3004,8 +3046,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="30">
-      <c r="A7" s="119"/>
-      <c r="B7" s="122"/>
+      <c r="A7" s="121"/>
+      <c r="B7" s="124"/>
       <c r="C7" s="5" t="s">
         <v>17</v>
       </c>
@@ -3026,8 +3068,8 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="30">
-      <c r="A8" s="119"/>
-      <c r="B8" s="122"/>
+      <c r="A8" s="121"/>
+      <c r="B8" s="124"/>
       <c r="C8" s="7" t="s">
         <v>19</v>
       </c>
@@ -3048,8 +3090,8 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="30">
-      <c r="A9" s="119"/>
-      <c r="B9" s="122"/>
+      <c r="A9" s="121"/>
+      <c r="B9" s="124"/>
       <c r="C9" s="7" t="s">
         <v>20</v>
       </c>
@@ -3070,8 +3112,8 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="30">
-      <c r="A10" s="119"/>
-      <c r="B10" s="122"/>
+      <c r="A10" s="121"/>
+      <c r="B10" s="124"/>
       <c r="C10" s="7" t="s">
         <v>22</v>
       </c>
@@ -3092,8 +3134,8 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="45">
-      <c r="A11" s="119"/>
-      <c r="B11" s="122"/>
+      <c r="A11" s="121"/>
+      <c r="B11" s="124"/>
       <c r="C11" s="7" t="s">
         <v>24</v>
       </c>
@@ -3114,8 +3156,8 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="30">
-      <c r="A12" s="119"/>
-      <c r="B12" s="122"/>
+      <c r="A12" s="121"/>
+      <c r="B12" s="124"/>
       <c r="C12" s="7" t="s">
         <v>25</v>
       </c>
@@ -3136,8 +3178,8 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="30">
-      <c r="A13" s="119"/>
-      <c r="B13" s="122"/>
+      <c r="A13" s="121"/>
+      <c r="B13" s="124"/>
       <c r="C13" s="7" t="s">
         <v>26</v>
       </c>
@@ -3158,8 +3200,8 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="90.95" thickBot="1">
-      <c r="A14" s="119"/>
-      <c r="B14" s="123"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="125"/>
       <c r="C14" s="14" t="s">
         <v>27</v>
       </c>
@@ -3180,8 +3222,8 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="45">
-      <c r="A15" s="119"/>
-      <c r="B15" s="124" t="s">
+      <c r="A15" s="121"/>
+      <c r="B15" s="126" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -3201,8 +3243,8 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="105">
-      <c r="A16" s="119"/>
-      <c r="B16" s="114"/>
+      <c r="A16" s="121"/>
+      <c r="B16" s="116"/>
       <c r="C16" s="5" t="s">
         <v>31</v>
       </c>
@@ -3220,8 +3262,8 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="30">
-      <c r="A17" s="119"/>
-      <c r="B17" s="114"/>
+      <c r="A17" s="121"/>
+      <c r="B17" s="116"/>
       <c r="C17" s="5" t="s">
         <v>32</v>
       </c>
@@ -3239,8 +3281,8 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="45">
-      <c r="A18" s="119"/>
-      <c r="B18" s="114"/>
+      <c r="A18" s="121"/>
+      <c r="B18" s="116"/>
       <c r="C18" s="5" t="s">
         <v>33</v>
       </c>
@@ -3258,8 +3300,8 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="45">
-      <c r="A19" s="119"/>
-      <c r="B19" s="114"/>
+      <c r="A19" s="121"/>
+      <c r="B19" s="116"/>
       <c r="C19" s="5" t="s">
         <v>34</v>
       </c>
@@ -3277,8 +3319,8 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="45.95" thickBot="1">
-      <c r="A20" s="119"/>
-      <c r="B20" s="115"/>
+      <c r="A20" s="121"/>
+      <c r="B20" s="117"/>
       <c r="C20" s="14" t="s">
         <v>35</v>
       </c>
@@ -3296,8 +3338,8 @@
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="119"/>
-      <c r="B21" s="124" t="s">
+      <c r="A21" s="121"/>
+      <c r="B21" s="126" t="s">
         <v>36</v>
       </c>
       <c r="C21" s="3" t="s">
@@ -3317,8 +3359,8 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="30">
-      <c r="A22" s="119"/>
-      <c r="B22" s="114"/>
+      <c r="A22" s="121"/>
+      <c r="B22" s="116"/>
       <c r="C22" s="5" t="s">
         <v>38</v>
       </c>
@@ -3336,8 +3378,8 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="45">
-      <c r="A23" s="119"/>
-      <c r="B23" s="114"/>
+      <c r="A23" s="121"/>
+      <c r="B23" s="116"/>
       <c r="C23" s="5" t="s">
         <v>39</v>
       </c>
@@ -3355,8 +3397,8 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="30">
-      <c r="A24" s="119"/>
-      <c r="B24" s="114"/>
+      <c r="A24" s="121"/>
+      <c r="B24" s="116"/>
       <c r="C24" s="5" t="s">
         <v>40</v>
       </c>
@@ -3374,8 +3416,8 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="60">
-      <c r="A25" s="119"/>
-      <c r="B25" s="114"/>
+      <c r="A25" s="121"/>
+      <c r="B25" s="116"/>
       <c r="C25" s="5" t="s">
         <v>41</v>
       </c>
@@ -3393,8 +3435,8 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="60.95" thickBot="1">
-      <c r="A26" s="119"/>
-      <c r="B26" s="125"/>
+      <c r="A26" s="121"/>
+      <c r="B26" s="127"/>
       <c r="C26" s="8" t="s">
         <v>42</v>
       </c>
@@ -3412,8 +3454,8 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="45.95">
-      <c r="A27" s="119"/>
-      <c r="B27" s="124" t="s">
+      <c r="A27" s="121"/>
+      <c r="B27" s="126" t="s">
         <v>43</v>
       </c>
       <c r="C27" s="10" t="s">
@@ -3433,8 +3475,8 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="60.95">
-      <c r="A28" s="119"/>
-      <c r="B28" s="114"/>
+      <c r="A28" s="121"/>
+      <c r="B28" s="116"/>
       <c r="C28" s="11" t="s">
         <v>45</v>
       </c>
@@ -3452,8 +3494,8 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="60.95">
-      <c r="A29" s="119"/>
-      <c r="B29" s="114"/>
+      <c r="A29" s="121"/>
+      <c r="B29" s="116"/>
       <c r="C29" s="11" t="s">
         <v>46</v>
       </c>
@@ -3471,8 +3513,8 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="30.95">
-      <c r="A30" s="119"/>
-      <c r="B30" s="114"/>
+      <c r="A30" s="121"/>
+      <c r="B30" s="116"/>
       <c r="C30" s="11" t="s">
         <v>47</v>
       </c>
@@ -3490,8 +3532,8 @@
       </c>
     </row>
     <row r="31" spans="1:7" ht="60.95">
-      <c r="A31" s="119"/>
-      <c r="B31" s="114"/>
+      <c r="A31" s="121"/>
+      <c r="B31" s="116"/>
       <c r="C31" s="11" t="s">
         <v>48</v>
       </c>
@@ -3509,8 +3551,8 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="45.95">
-      <c r="A32" s="119"/>
-      <c r="B32" s="114"/>
+      <c r="A32" s="121"/>
+      <c r="B32" s="116"/>
       <c r="C32" s="11" t="s">
         <v>49</v>
       </c>
@@ -3528,8 +3570,8 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="45.95">
-      <c r="A33" s="119"/>
-      <c r="B33" s="114"/>
+      <c r="A33" s="121"/>
+      <c r="B33" s="116"/>
       <c r="C33" s="11" t="s">
         <v>50</v>
       </c>
@@ -3547,8 +3589,8 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="45.95">
-      <c r="A34" s="119"/>
-      <c r="B34" s="114"/>
+      <c r="A34" s="121"/>
+      <c r="B34" s="116"/>
       <c r="C34" s="11" t="s">
         <v>51</v>
       </c>
@@ -3566,8 +3608,8 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="30">
-      <c r="A35" s="119"/>
-      <c r="B35" s="114"/>
+      <c r="A35" s="121"/>
+      <c r="B35" s="116"/>
       <c r="C35" s="5" t="s">
         <v>52</v>
       </c>
@@ -3585,8 +3627,8 @@
       </c>
     </row>
     <row r="36" spans="1:7" ht="60">
-      <c r="A36" s="119"/>
-      <c r="B36" s="114"/>
+      <c r="A36" s="121"/>
+      <c r="B36" s="116"/>
       <c r="C36" s="7" t="s">
         <v>53</v>
       </c>
@@ -3604,8 +3646,8 @@
       </c>
     </row>
     <row r="37" spans="1:7" ht="30.95" thickBot="1">
-      <c r="A37" s="119"/>
-      <c r="B37" s="115"/>
+      <c r="A37" s="121"/>
+      <c r="B37" s="117"/>
       <c r="C37" s="16" t="s">
         <v>54</v>
       </c>
@@ -3623,8 +3665,8 @@
       </c>
     </row>
     <row r="38" spans="1:7" ht="30.95">
-      <c r="A38" s="119"/>
-      <c r="B38" s="126" t="s">
+      <c r="A38" s="121"/>
+      <c r="B38" s="128" t="s">
         <v>55</v>
       </c>
       <c r="C38" s="17" t="s">
@@ -3644,8 +3686,8 @@
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="119"/>
-      <c r="B39" s="122"/>
+      <c r="A39" s="121"/>
+      <c r="B39" s="124"/>
       <c r="C39" s="11" t="s">
         <v>57</v>
       </c>
@@ -3663,8 +3705,8 @@
       </c>
     </row>
     <row r="40" spans="1:7" ht="30.95">
-      <c r="A40" s="119"/>
-      <c r="B40" s="122"/>
+      <c r="A40" s="121"/>
+      <c r="B40" s="124"/>
       <c r="C40" s="11" t="s">
         <v>58</v>
       </c>
@@ -3682,8 +3724,8 @@
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="119"/>
-      <c r="B41" s="122"/>
+      <c r="A41" s="121"/>
+      <c r="B41" s="124"/>
       <c r="C41" s="11" t="s">
         <v>59</v>
       </c>
@@ -3701,8 +3743,8 @@
       </c>
     </row>
     <row r="42" spans="1:7" ht="32.1" thickBot="1">
-      <c r="A42" s="119"/>
-      <c r="B42" s="123"/>
+      <c r="A42" s="121"/>
+      <c r="B42" s="125"/>
       <c r="C42" s="19" t="s">
         <v>60</v>
       </c>
@@ -3720,8 +3762,8 @@
       </c>
     </row>
     <row r="43" spans="1:7" ht="30">
-      <c r="A43" s="119"/>
-      <c r="B43" s="127" t="s">
+      <c r="A43" s="121"/>
+      <c r="B43" s="129" t="s">
         <v>61</v>
       </c>
       <c r="C43" s="3" t="s">
@@ -3741,8 +3783,8 @@
       </c>
     </row>
     <row r="44" spans="1:7" ht="30">
-      <c r="A44" s="119"/>
-      <c r="B44" s="128"/>
+      <c r="A44" s="121"/>
+      <c r="B44" s="130"/>
       <c r="C44" s="5" t="s">
         <v>63</v>
       </c>
@@ -3760,8 +3802,8 @@
       </c>
     </row>
     <row r="45" spans="1:7" ht="45">
-      <c r="A45" s="119"/>
-      <c r="B45" s="128"/>
+      <c r="A45" s="121"/>
+      <c r="B45" s="130"/>
       <c r="C45" s="5" t="s">
         <v>64</v>
       </c>
@@ -3779,8 +3821,8 @@
       </c>
     </row>
     <row r="46" spans="1:7" ht="45">
-      <c r="A46" s="119"/>
-      <c r="B46" s="128"/>
+      <c r="A46" s="121"/>
+      <c r="B46" s="130"/>
       <c r="C46" s="5" t="s">
         <v>65</v>
       </c>
@@ -3798,8 +3840,8 @@
       </c>
     </row>
     <row r="47" spans="1:7" ht="30">
-      <c r="A47" s="119"/>
-      <c r="B47" s="128"/>
+      <c r="A47" s="121"/>
+      <c r="B47" s="130"/>
       <c r="C47" s="13" t="s">
         <v>66</v>
       </c>
@@ -3817,8 +3859,8 @@
       </c>
     </row>
     <row r="48" spans="1:7" ht="30">
-      <c r="A48" s="119"/>
-      <c r="B48" s="128"/>
+      <c r="A48" s="121"/>
+      <c r="B48" s="130"/>
       <c r="C48" s="5" t="s">
         <v>67</v>
       </c>
@@ -3836,8 +3878,8 @@
       </c>
     </row>
     <row r="49" spans="1:7" ht="30.95" thickBot="1">
-      <c r="A49" s="119"/>
-      <c r="B49" s="128"/>
+      <c r="A49" s="121"/>
+      <c r="B49" s="130"/>
       <c r="C49" s="8" t="s">
         <v>68</v>
       </c>
@@ -3855,8 +3897,8 @@
       </c>
     </row>
     <row r="50" spans="1:7" ht="30">
-      <c r="A50" s="119"/>
-      <c r="B50" s="124" t="s">
+      <c r="A50" s="121"/>
+      <c r="B50" s="126" t="s">
         <v>69</v>
       </c>
       <c r="C50" s="3" t="s">
@@ -3876,8 +3918,8 @@
       </c>
     </row>
     <row r="51" spans="1:7" ht="30">
-      <c r="A51" s="119"/>
-      <c r="B51" s="114"/>
+      <c r="A51" s="121"/>
+      <c r="B51" s="116"/>
       <c r="C51" s="5" t="s">
         <v>71</v>
       </c>
@@ -3895,8 +3937,8 @@
       </c>
     </row>
     <row r="52" spans="1:7" ht="30.95">
-      <c r="A52" s="119"/>
-      <c r="B52" s="114"/>
+      <c r="A52" s="121"/>
+      <c r="B52" s="116"/>
       <c r="C52" s="11" t="s">
         <v>72</v>
       </c>
@@ -3914,8 +3956,8 @@
       </c>
     </row>
     <row r="53" spans="1:7" ht="30.95">
-      <c r="A53" s="119"/>
-      <c r="B53" s="114"/>
+      <c r="A53" s="121"/>
+      <c r="B53" s="116"/>
       <c r="C53" s="11" t="s">
         <v>73</v>
       </c>
@@ -3933,8 +3975,8 @@
       </c>
     </row>
     <row r="54" spans="1:7" ht="30.95">
-      <c r="A54" s="119"/>
-      <c r="B54" s="114"/>
+      <c r="A54" s="121"/>
+      <c r="B54" s="116"/>
       <c r="C54" s="11" t="s">
         <v>74</v>
       </c>
@@ -3952,8 +3994,8 @@
       </c>
     </row>
     <row r="55" spans="1:7" ht="32.1" thickBot="1">
-      <c r="A55" s="119"/>
-      <c r="B55" s="115"/>
+      <c r="A55" s="121"/>
+      <c r="B55" s="117"/>
       <c r="C55" s="19" t="s">
         <v>75</v>
       </c>
@@ -3971,8 +4013,8 @@
       </c>
     </row>
     <row r="56" spans="1:7" ht="30.95">
-      <c r="A56" s="119"/>
-      <c r="B56" s="113" t="s">
+      <c r="A56" s="121"/>
+      <c r="B56" s="115" t="s">
         <v>76</v>
       </c>
       <c r="C56" s="17" t="s">
@@ -3992,8 +4034,8 @@
       </c>
     </row>
     <row r="57" spans="1:7" ht="30">
-      <c r="A57" s="119"/>
-      <c r="B57" s="114"/>
+      <c r="A57" s="121"/>
+      <c r="B57" s="116"/>
       <c r="C57" s="5" t="s">
         <v>78</v>
       </c>
@@ -4011,8 +4053,8 @@
       </c>
     </row>
     <row r="58" spans="1:7" ht="105">
-      <c r="A58" s="119"/>
-      <c r="B58" s="114"/>
+      <c r="A58" s="121"/>
+      <c r="B58" s="116"/>
       <c r="C58" s="5" t="s">
         <v>79</v>
       </c>
@@ -4030,8 +4072,8 @@
       </c>
     </row>
     <row r="59" spans="1:7" ht="45.95">
-      <c r="A59" s="119"/>
-      <c r="B59" s="114"/>
+      <c r="A59" s="121"/>
+      <c r="B59" s="116"/>
       <c r="C59" s="11" t="s">
         <v>80</v>
       </c>
@@ -4049,8 +4091,8 @@
       </c>
     </row>
     <row r="60" spans="1:7" ht="30">
-      <c r="A60" s="119"/>
-      <c r="B60" s="114"/>
+      <c r="A60" s="121"/>
+      <c r="B60" s="116"/>
       <c r="C60" s="5" t="s">
         <v>81</v>
       </c>
@@ -4068,8 +4110,8 @@
       </c>
     </row>
     <row r="61" spans="1:7" ht="75">
-      <c r="A61" s="119"/>
-      <c r="B61" s="114"/>
+      <c r="A61" s="121"/>
+      <c r="B61" s="116"/>
       <c r="C61" s="5" t="s">
         <v>82</v>
       </c>
@@ -4087,8 +4129,8 @@
       </c>
     </row>
     <row r="62" spans="1:7" ht="62.1" thickBot="1">
-      <c r="A62" s="119"/>
-      <c r="B62" s="115"/>
+      <c r="A62" s="121"/>
+      <c r="B62" s="117"/>
       <c r="C62" s="12" t="s">
         <v>83</v>
       </c>
@@ -4106,8 +4148,8 @@
       </c>
     </row>
     <row r="63" spans="1:7" ht="30">
-      <c r="A63" s="119"/>
-      <c r="B63" s="116" t="s">
+      <c r="A63" s="121"/>
+      <c r="B63" s="118" t="s">
         <v>84</v>
       </c>
       <c r="C63" s="23" t="s">
@@ -4127,8 +4169,8 @@
       </c>
     </row>
     <row r="64" spans="1:7" ht="30">
-      <c r="A64" s="119"/>
-      <c r="B64" s="117"/>
+      <c r="A64" s="121"/>
+      <c r="B64" s="119"/>
       <c r="C64" s="24" t="s">
         <v>86</v>
       </c>
@@ -4146,8 +4188,8 @@
       </c>
     </row>
     <row r="65" spans="1:7" ht="45">
-      <c r="A65" s="119"/>
-      <c r="B65" s="117"/>
+      <c r="A65" s="121"/>
+      <c r="B65" s="119"/>
       <c r="C65" s="24" t="s">
         <v>87</v>
       </c>
@@ -4165,8 +4207,8 @@
       </c>
     </row>
     <row r="66" spans="1:7" ht="30">
-      <c r="A66" s="119"/>
-      <c r="B66" s="117"/>
+      <c r="A66" s="121"/>
+      <c r="B66" s="119"/>
       <c r="C66" s="24" t="s">
         <v>88</v>
       </c>
@@ -4184,8 +4226,8 @@
       </c>
     </row>
     <row r="67" spans="1:7" ht="30">
-      <c r="A67" s="119"/>
-      <c r="B67" s="117"/>
+      <c r="A67" s="121"/>
+      <c r="B67" s="119"/>
       <c r="C67" s="24" t="s">
         <v>89</v>
       </c>
@@ -4203,8 +4245,8 @@
       </c>
     </row>
     <row r="68" spans="1:7" ht="30">
-      <c r="A68" s="119"/>
-      <c r="B68" s="117"/>
+      <c r="A68" s="121"/>
+      <c r="B68" s="119"/>
       <c r="C68" s="24" t="s">
         <v>90</v>
       </c>
@@ -4222,8 +4264,8 @@
       </c>
     </row>
     <row r="69" spans="1:7" ht="30">
-      <c r="A69" s="119"/>
-      <c r="B69" s="117"/>
+      <c r="A69" s="121"/>
+      <c r="B69" s="119"/>
       <c r="C69" s="24" t="s">
         <v>91</v>
       </c>
@@ -4241,8 +4283,8 @@
       </c>
     </row>
     <row r="70" spans="1:7" ht="30.95" thickBot="1">
-      <c r="A70" s="120"/>
-      <c r="B70" s="118"/>
+      <c r="A70" s="122"/>
+      <c r="B70" s="120"/>
       <c r="C70" s="25" t="s">
         <v>92</v>
       </c>
@@ -4317,24 +4359,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.100000000000001" thickBot="1">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="135" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="135" t="s">
+      <c r="A2" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="139" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="137" t="s">
+      <c r="C2" s="139" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="28" t="s">
@@ -4351,9 +4393,9 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="110"/>
-      <c r="B3" s="111"/>
-      <c r="C3" s="111"/>
+      <c r="A3" s="112"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="113"/>
       <c r="D3" s="1" t="str">
         <f>'[1]Scenario overview'!B6</f>
         <v>A high-burden country close to reaching 95s across all populations</v>
@@ -4372,9 +4414,9 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="17.100000000000001" thickBot="1">
-      <c r="A4" s="136"/>
-      <c r="B4" s="138"/>
-      <c r="C4" s="138"/>
+      <c r="A4" s="138"/>
+      <c r="B4" s="140"/>
+      <c r="C4" s="140"/>
       <c r="D4" s="29" t="str">
         <f>'[1]Scenario overview'!C6</f>
         <v>Limited, possibly some unsuppressed ART clients and some specific sub-segments that are generally underserved</v>
@@ -4393,7 +4435,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="17.100000000000001" thickBot="1">
-      <c r="A5" s="129" t="s">
+      <c r="A5" s="131" t="s">
         <v>94</v>
       </c>
       <c r="B5" s="26" t="s">
@@ -4416,8 +4458,8 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="130"/>
-      <c r="B6" s="124" t="s">
+      <c r="A6" s="132"/>
+      <c r="B6" s="126" t="s">
         <v>97</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -4437,8 +4479,8 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="130"/>
-      <c r="B7" s="122"/>
+      <c r="A7" s="132"/>
+      <c r="B7" s="124"/>
       <c r="C7" s="6" t="s">
         <v>99</v>
       </c>
@@ -4456,8 +4498,8 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="130"/>
-      <c r="B8" s="122"/>
+      <c r="A8" s="132"/>
+      <c r="B8" s="124"/>
       <c r="C8" s="6" t="s">
         <v>100</v>
       </c>
@@ -4475,8 +4517,8 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="130"/>
-      <c r="B9" s="122"/>
+      <c r="A9" s="132"/>
+      <c r="B9" s="124"/>
       <c r="C9" s="6" t="s">
         <v>101</v>
       </c>
@@ -4494,8 +4536,8 @@
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="130"/>
-      <c r="B10" s="122"/>
+      <c r="A10" s="132"/>
+      <c r="B10" s="124"/>
       <c r="C10" s="6" t="s">
         <v>102</v>
       </c>
@@ -4513,8 +4555,8 @@
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="130"/>
-      <c r="B11" s="122"/>
+      <c r="A11" s="132"/>
+      <c r="B11" s="124"/>
       <c r="C11" s="6" t="s">
         <v>103</v>
       </c>
@@ -4532,8 +4574,8 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="130"/>
-      <c r="B12" s="122"/>
+      <c r="A12" s="132"/>
+      <c r="B12" s="124"/>
       <c r="C12" s="6" t="s">
         <v>104</v>
       </c>
@@ -4551,8 +4593,8 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="130"/>
-      <c r="B13" s="122"/>
+      <c r="A13" s="132"/>
+      <c r="B13" s="124"/>
       <c r="C13" s="6" t="s">
         <v>105</v>
       </c>
@@ -4570,8 +4612,8 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="130"/>
-      <c r="B14" s="122"/>
+      <c r="A14" s="132"/>
+      <c r="B14" s="124"/>
       <c r="C14" s="6" t="s">
         <v>106</v>
       </c>
@@ -4589,8 +4631,8 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="130"/>
-      <c r="B15" s="122"/>
+      <c r="A15" s="132"/>
+      <c r="B15" s="124"/>
       <c r="C15" s="6" t="s">
         <v>107</v>
       </c>
@@ -4608,8 +4650,8 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="130"/>
-      <c r="B16" s="122"/>
+      <c r="A16" s="132"/>
+      <c r="B16" s="124"/>
       <c r="C16" s="6" t="s">
         <v>108</v>
       </c>
@@ -4627,8 +4669,8 @@
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="130"/>
-      <c r="B17" s="122"/>
+      <c r="A17" s="132"/>
+      <c r="B17" s="124"/>
       <c r="C17" s="6" t="s">
         <v>109</v>
       </c>
@@ -4646,8 +4688,8 @@
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="130"/>
-      <c r="B18" s="122"/>
+      <c r="A18" s="132"/>
+      <c r="B18" s="124"/>
       <c r="C18" s="6" t="s">
         <v>110</v>
       </c>
@@ -4665,8 +4707,8 @@
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="130"/>
-      <c r="B19" s="122"/>
+      <c r="A19" s="132"/>
+      <c r="B19" s="124"/>
       <c r="C19" s="6" t="s">
         <v>111</v>
       </c>
@@ -4684,8 +4726,8 @@
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="130"/>
-      <c r="B20" s="122"/>
+      <c r="A20" s="132"/>
+      <c r="B20" s="124"/>
       <c r="C20" s="6" t="s">
         <v>112</v>
       </c>
@@ -4703,8 +4745,8 @@
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="130"/>
-      <c r="B21" s="122"/>
+      <c r="A21" s="132"/>
+      <c r="B21" s="124"/>
       <c r="C21" s="6" t="s">
         <v>113</v>
       </c>
@@ -4722,8 +4764,8 @@
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="130"/>
-      <c r="B22" s="122"/>
+      <c r="A22" s="132"/>
+      <c r="B22" s="124"/>
       <c r="C22" s="6" t="s">
         <v>114</v>
       </c>
@@ -4741,8 +4783,8 @@
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="130"/>
-      <c r="B23" s="122"/>
+      <c r="A23" s="132"/>
+      <c r="B23" s="124"/>
       <c r="C23" s="6" t="s">
         <v>115</v>
       </c>
@@ -4760,8 +4802,8 @@
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="130"/>
-      <c r="B24" s="122"/>
+      <c r="A24" s="132"/>
+      <c r="B24" s="124"/>
       <c r="C24" s="6" t="s">
         <v>116</v>
       </c>
@@ -4779,8 +4821,8 @@
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="130"/>
-      <c r="B25" s="122"/>
+      <c r="A25" s="132"/>
+      <c r="B25" s="124"/>
       <c r="C25" s="6" t="s">
         <v>117</v>
       </c>
@@ -4798,8 +4840,8 @@
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="130"/>
-      <c r="B26" s="122"/>
+      <c r="A26" s="132"/>
+      <c r="B26" s="124"/>
       <c r="C26" s="6" t="s">
         <v>118</v>
       </c>
@@ -4817,8 +4859,8 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="17.100000000000001" thickBot="1">
-      <c r="A27" s="130"/>
-      <c r="B27" s="123"/>
+      <c r="A27" s="132"/>
+      <c r="B27" s="125"/>
       <c r="C27" s="15" t="s">
         <v>119</v>
       </c>
@@ -4836,8 +4878,8 @@
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="130"/>
-      <c r="B28" s="124" t="s">
+      <c r="A28" s="132"/>
+      <c r="B28" s="126" t="s">
         <v>120</v>
       </c>
       <c r="C28" s="4" t="s">
@@ -4857,8 +4899,8 @@
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="130"/>
-      <c r="B29" s="114"/>
+      <c r="A29" s="132"/>
+      <c r="B29" s="116"/>
       <c r="C29" s="6" t="s">
         <v>122</v>
       </c>
@@ -4876,8 +4918,8 @@
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="130"/>
-      <c r="B30" s="114"/>
+      <c r="A30" s="132"/>
+      <c r="B30" s="116"/>
       <c r="C30" s="6" t="s">
         <v>123</v>
       </c>
@@ -4895,8 +4937,8 @@
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="130"/>
-      <c r="B31" s="114"/>
+      <c r="A31" s="132"/>
+      <c r="B31" s="116"/>
       <c r="C31" s="6" t="s">
         <v>124</v>
       </c>
@@ -4914,8 +4956,8 @@
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="130"/>
-      <c r="B32" s="114"/>
+      <c r="A32" s="132"/>
+      <c r="B32" s="116"/>
       <c r="C32" s="6" t="s">
         <v>125</v>
       </c>
@@ -4933,8 +4975,8 @@
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="130"/>
-      <c r="B33" s="114"/>
+      <c r="A33" s="132"/>
+      <c r="B33" s="116"/>
       <c r="C33" s="6" t="s">
         <v>126</v>
       </c>
@@ -4952,8 +4994,8 @@
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="130"/>
-      <c r="B34" s="114"/>
+      <c r="A34" s="132"/>
+      <c r="B34" s="116"/>
       <c r="C34" s="6" t="s">
         <v>127</v>
       </c>
@@ -4971,8 +5013,8 @@
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="130"/>
-      <c r="B35" s="114"/>
+      <c r="A35" s="132"/>
+      <c r="B35" s="116"/>
       <c r="C35" s="6" t="s">
         <v>128</v>
       </c>
@@ -4990,8 +5032,8 @@
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="130"/>
-      <c r="B36" s="114"/>
+      <c r="A36" s="132"/>
+      <c r="B36" s="116"/>
       <c r="C36" s="6" t="s">
         <v>129</v>
       </c>
@@ -5009,8 +5051,8 @@
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="130"/>
-      <c r="B37" s="114"/>
+      <c r="A37" s="132"/>
+      <c r="B37" s="116"/>
       <c r="C37" s="6" t="s">
         <v>130</v>
       </c>
@@ -5028,8 +5070,8 @@
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="130"/>
-      <c r="B38" s="114"/>
+      <c r="A38" s="132"/>
+      <c r="B38" s="116"/>
       <c r="C38" s="6" t="s">
         <v>131</v>
       </c>
@@ -5047,8 +5089,8 @@
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="130"/>
-      <c r="B39" s="114"/>
+      <c r="A39" s="132"/>
+      <c r="B39" s="116"/>
       <c r="C39" s="6" t="s">
         <v>133</v>
       </c>
@@ -5066,8 +5108,8 @@
       </c>
     </row>
     <row r="40" spans="1:7" ht="17.100000000000001" thickBot="1">
-      <c r="A40" s="130"/>
-      <c r="B40" s="125"/>
+      <c r="A40" s="132"/>
+      <c r="B40" s="127"/>
       <c r="C40" s="9" t="s">
         <v>134</v>
       </c>
@@ -5085,8 +5127,8 @@
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="131"/>
-      <c r="B41" s="124" t="s">
+      <c r="A41" s="133"/>
+      <c r="B41" s="126" t="s">
         <v>135</v>
       </c>
       <c r="C41" s="4" t="s">
@@ -5106,8 +5148,8 @@
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="131"/>
-      <c r="B42" s="114"/>
+      <c r="A42" s="133"/>
+      <c r="B42" s="116"/>
       <c r="C42" s="6" t="s">
         <v>137</v>
       </c>
@@ -5125,8 +5167,8 @@
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="131"/>
-      <c r="B43" s="114"/>
+      <c r="A43" s="133"/>
+      <c r="B43" s="116"/>
       <c r="C43" s="6" t="s">
         <v>138</v>
       </c>
@@ -5144,8 +5186,8 @@
       </c>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="131"/>
-      <c r="B44" s="114"/>
+      <c r="A44" s="133"/>
+      <c r="B44" s="116"/>
       <c r="C44" s="6" t="s">
         <v>139</v>
       </c>
@@ -5163,8 +5205,8 @@
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="131"/>
-      <c r="B45" s="114"/>
+      <c r="A45" s="133"/>
+      <c r="B45" s="116"/>
       <c r="C45" s="6" t="s">
         <v>140</v>
       </c>
@@ -5182,8 +5224,8 @@
       </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="131"/>
-      <c r="B46" s="114"/>
+      <c r="A46" s="133"/>
+      <c r="B46" s="116"/>
       <c r="C46" s="6" t="s">
         <v>141</v>
       </c>
@@ -5201,8 +5243,8 @@
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="131"/>
-      <c r="B47" s="114"/>
+      <c r="A47" s="133"/>
+      <c r="B47" s="116"/>
       <c r="C47" s="6" t="s">
         <v>142</v>
       </c>
@@ -5220,8 +5262,8 @@
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="131"/>
-      <c r="B48" s="114"/>
+      <c r="A48" s="133"/>
+      <c r="B48" s="116"/>
       <c r="C48" s="6" t="s">
         <v>143</v>
       </c>
@@ -5239,8 +5281,8 @@
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="131"/>
-      <c r="B49" s="114"/>
+      <c r="A49" s="133"/>
+      <c r="B49" s="116"/>
       <c r="C49" s="6" t="s">
         <v>144</v>
       </c>
@@ -5258,8 +5300,8 @@
       </c>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="131"/>
-      <c r="B50" s="114"/>
+      <c r="A50" s="133"/>
+      <c r="B50" s="116"/>
       <c r="C50" s="6" t="s">
         <v>145</v>
       </c>
@@ -5277,8 +5319,8 @@
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="131"/>
-      <c r="B51" s="114"/>
+      <c r="A51" s="133"/>
+      <c r="B51" s="116"/>
       <c r="C51" s="6" t="s">
         <v>146</v>
       </c>
@@ -5296,8 +5338,8 @@
       </c>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="131"/>
-      <c r="B52" s="114"/>
+      <c r="A52" s="133"/>
+      <c r="B52" s="116"/>
       <c r="C52" s="6" t="s">
         <v>147</v>
       </c>
@@ -5315,8 +5357,8 @@
       </c>
     </row>
     <row r="53" spans="1:7" ht="17.100000000000001" thickBot="1">
-      <c r="A53" s="131"/>
-      <c r="B53" s="115"/>
+      <c r="A53" s="133"/>
+      <c r="B53" s="117"/>
       <c r="C53" s="33" t="s">
         <v>148</v>
       </c>
@@ -5334,7 +5376,7 @@
       </c>
     </row>
     <row r="54" spans="1:7" ht="17.100000000000001" thickBot="1">
-      <c r="A54" s="132"/>
+      <c r="A54" s="134"/>
       <c r="B54" s="27" t="s">
         <v>149</v>
       </c>
@@ -5406,20 +5448,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.100000000000001" thickBot="1">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="141" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="140"/>
-      <c r="B2" s="142"/>
-      <c r="C2" s="137"/>
+      <c r="A2" s="142"/>
+      <c r="B2" s="144"/>
+      <c r="C2" s="139"/>
       <c r="D2" s="28" t="s">
         <v>3</v>
       </c>
@@ -5434,9 +5476,9 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="141"/>
-      <c r="B3" s="143"/>
-      <c r="C3" s="111"/>
+      <c r="A3" s="143"/>
+      <c r="B3" s="145"/>
+      <c r="C3" s="113"/>
       <c r="D3" s="1" t="str">
         <f>'[1]Scenario overview'!B6</f>
         <v>A high-burden country close to reaching 95s across all populations</v>
@@ -5455,9 +5497,9 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="17.100000000000001" thickBot="1">
-      <c r="A4" s="141"/>
-      <c r="B4" s="144"/>
-      <c r="C4" s="112"/>
+      <c r="A4" s="143"/>
+      <c r="B4" s="146"/>
+      <c r="C4" s="114"/>
       <c r="D4" s="2" t="str">
         <f>'[1]Scenario overview'!C6</f>
         <v>Limited, possibly some unsuppressed ART clients and some specific sub-segments that are generally underserved</v>
@@ -5476,10 +5518,10 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="119" t="s">
+      <c r="A5" s="121" t="s">
         <v>152</v>
       </c>
-      <c r="B5" s="124" t="s">
+      <c r="B5" s="126" t="s">
         <v>153</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -5499,8 +5541,8 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="119"/>
-      <c r="B6" s="114"/>
+      <c r="A6" s="121"/>
+      <c r="B6" s="116"/>
       <c r="C6" s="6" t="s">
         <v>155</v>
       </c>
@@ -5518,8 +5560,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="17.100000000000001" thickBot="1">
-      <c r="A7" s="119"/>
-      <c r="B7" s="115"/>
+      <c r="A7" s="121"/>
+      <c r="B7" s="117"/>
       <c r="C7" s="15" t="s">
         <v>156</v>
       </c>
@@ -5537,8 +5579,8 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="119"/>
-      <c r="B8" s="124" t="s">
+      <c r="A8" s="121"/>
+      <c r="B8" s="126" t="s">
         <v>157</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -5558,8 +5600,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="17.100000000000001" thickBot="1">
-      <c r="A9" s="119"/>
-      <c r="B9" s="115"/>
+      <c r="A9" s="121"/>
+      <c r="B9" s="117"/>
       <c r="C9" s="15" t="s">
         <v>159</v>
       </c>
@@ -5577,8 +5619,8 @@
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="119"/>
-      <c r="B10" s="124" t="s">
+      <c r="A10" s="121"/>
+      <c r="B10" s="126" t="s">
         <v>160</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -5598,8 +5640,8 @@
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="119"/>
-      <c r="B11" s="114"/>
+      <c r="A11" s="121"/>
+      <c r="B11" s="116"/>
       <c r="C11" s="6" t="s">
         <v>162</v>
       </c>
@@ -5617,8 +5659,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="17.100000000000001" thickBot="1">
-      <c r="A12" s="119"/>
-      <c r="B12" s="115"/>
+      <c r="A12" s="121"/>
+      <c r="B12" s="117"/>
       <c r="C12" s="15" t="s">
         <v>163</v>
       </c>
@@ -5636,8 +5678,8 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="119"/>
-      <c r="B13" s="124" t="s">
+      <c r="A13" s="121"/>
+      <c r="B13" s="126" t="s">
         <v>164</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -5657,8 +5699,8 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="119"/>
-      <c r="B14" s="114"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="116"/>
       <c r="C14" s="6" t="s">
         <v>166</v>
       </c>
@@ -5676,8 +5718,8 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="119"/>
-      <c r="B15" s="114"/>
+      <c r="A15" s="121"/>
+      <c r="B15" s="116"/>
       <c r="C15" s="6" t="s">
         <v>167</v>
       </c>
@@ -5695,8 +5737,8 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="119"/>
-      <c r="B16" s="114"/>
+      <c r="A16" s="121"/>
+      <c r="B16" s="116"/>
       <c r="C16" s="6" t="s">
         <v>168</v>
       </c>
@@ -5714,8 +5756,8 @@
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="119"/>
-      <c r="B17" s="114"/>
+      <c r="A17" s="121"/>
+      <c r="B17" s="116"/>
       <c r="C17" s="6" t="s">
         <v>169</v>
       </c>
@@ -5733,8 +5775,8 @@
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="119"/>
-      <c r="B18" s="114"/>
+      <c r="A18" s="121"/>
+      <c r="B18" s="116"/>
       <c r="C18" s="34" t="s">
         <v>170</v>
       </c>
@@ -5752,8 +5794,8 @@
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="119"/>
-      <c r="B19" s="114"/>
+      <c r="A19" s="121"/>
+      <c r="B19" s="116"/>
       <c r="C19" s="6" t="s">
         <v>171</v>
       </c>
@@ -5771,8 +5813,8 @@
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="119"/>
-      <c r="B20" s="114"/>
+      <c r="A20" s="121"/>
+      <c r="B20" s="116"/>
       <c r="C20" s="6" t="s">
         <v>172</v>
       </c>
@@ -5790,8 +5832,8 @@
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="119"/>
-      <c r="B21" s="114"/>
+      <c r="A21" s="121"/>
+      <c r="B21" s="116"/>
       <c r="C21" s="6" t="s">
         <v>173</v>
       </c>
@@ -5809,8 +5851,8 @@
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="119"/>
-      <c r="B22" s="114"/>
+      <c r="A22" s="121"/>
+      <c r="B22" s="116"/>
       <c r="C22" s="6" t="s">
         <v>174</v>
       </c>
@@ -5828,8 +5870,8 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="17.100000000000001" thickBot="1">
-      <c r="A23" s="119"/>
-      <c r="B23" s="115"/>
+      <c r="A23" s="121"/>
+      <c r="B23" s="117"/>
       <c r="C23" s="15" t="s">
         <v>175</v>
       </c>
@@ -5847,8 +5889,8 @@
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="119"/>
-      <c r="B24" s="124" t="s">
+      <c r="A24" s="121"/>
+      <c r="B24" s="126" t="s">
         <v>176</v>
       </c>
       <c r="C24" s="4" t="s">
@@ -5868,8 +5910,8 @@
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="119"/>
-      <c r="B25" s="114"/>
+      <c r="A25" s="121"/>
+      <c r="B25" s="116"/>
       <c r="C25" s="6" t="s">
         <v>178</v>
       </c>
@@ -5887,8 +5929,8 @@
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="119"/>
-      <c r="B26" s="114"/>
+      <c r="A26" s="121"/>
+      <c r="B26" s="116"/>
       <c r="C26" s="6" t="s">
         <v>179</v>
       </c>
@@ -5906,8 +5948,8 @@
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="119"/>
-      <c r="B27" s="114"/>
+      <c r="A27" s="121"/>
+      <c r="B27" s="116"/>
       <c r="C27" s="6" t="s">
         <v>180</v>
       </c>
@@ -5925,8 +5967,8 @@
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="119"/>
-      <c r="B28" s="114"/>
+      <c r="A28" s="121"/>
+      <c r="B28" s="116"/>
       <c r="C28" s="6" t="s">
         <v>181</v>
       </c>
@@ -5944,8 +5986,8 @@
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="119"/>
-      <c r="B29" s="114"/>
+      <c r="A29" s="121"/>
+      <c r="B29" s="116"/>
       <c r="C29" s="6" t="s">
         <v>182</v>
       </c>
@@ -5963,8 +6005,8 @@
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="119"/>
-      <c r="B30" s="114"/>
+      <c r="A30" s="121"/>
+      <c r="B30" s="116"/>
       <c r="C30" s="6" t="s">
         <v>183</v>
       </c>
@@ -5982,8 +6024,8 @@
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="119"/>
-      <c r="B31" s="114"/>
+      <c r="A31" s="121"/>
+      <c r="B31" s="116"/>
       <c r="C31" s="6" t="s">
         <v>174</v>
       </c>
@@ -6001,8 +6043,8 @@
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="119"/>
-      <c r="B32" s="114"/>
+      <c r="A32" s="121"/>
+      <c r="B32" s="116"/>
       <c r="C32" s="6" t="s">
         <v>184</v>
       </c>
@@ -6020,8 +6062,8 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="17.100000000000001" thickBot="1">
-      <c r="A33" s="119"/>
-      <c r="B33" s="115"/>
+      <c r="A33" s="121"/>
+      <c r="B33" s="117"/>
       <c r="C33" s="15" t="s">
         <v>185</v>
       </c>
@@ -6039,8 +6081,8 @@
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="119"/>
-      <c r="B34" s="124" t="s">
+      <c r="A34" s="121"/>
+      <c r="B34" s="126" t="s">
         <v>186</v>
       </c>
       <c r="C34" s="35" t="s">
@@ -6060,8 +6102,8 @@
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="119"/>
-      <c r="B35" s="114"/>
+      <c r="A35" s="121"/>
+      <c r="B35" s="116"/>
       <c r="C35" s="36" t="s">
         <v>188</v>
       </c>
@@ -6079,8 +6121,8 @@
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="119"/>
-      <c r="B36" s="114"/>
+      <c r="A36" s="121"/>
+      <c r="B36" s="116"/>
       <c r="C36" s="6" t="s">
         <v>189</v>
       </c>
@@ -6098,8 +6140,8 @@
       </c>
     </row>
     <row r="37" spans="1:7" ht="17.100000000000001" thickBot="1">
-      <c r="A37" s="119"/>
-      <c r="B37" s="115"/>
+      <c r="A37" s="121"/>
+      <c r="B37" s="117"/>
       <c r="C37" s="15" t="s">
         <v>190</v>
       </c>
@@ -6117,7 +6159,7 @@
       </c>
     </row>
     <row r="38" spans="1:7" ht="17.100000000000001" thickBot="1">
-      <c r="A38" s="120"/>
+      <c r="A38" s="122"/>
       <c r="B38" s="26" t="s">
         <v>191</v>
       </c>
@@ -6179,7 +6221,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{572C777E-CA3B-2741-A6EF-7E74D6D879C4}">
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
@@ -6245,7 +6287,7 @@
       <c r="H4" s="55" t="s">
         <v>201</v>
       </c>
-      <c r="J4" s="147" t="s">
+      <c r="J4" s="111" t="s">
         <v>202</v>
       </c>
       <c r="K4" s="53" t="s">
@@ -6275,8 +6317,12 @@
       <c r="C6" s="72"/>
       <c r="D6" s="72"/>
       <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="72"/>
+      <c r="F6" s="72" t="s">
+        <v>201</v>
+      </c>
+      <c r="G6" s="72" t="s">
+        <v>201</v>
+      </c>
       <c r="H6" s="49"/>
       <c r="J6" s="52"/>
     </row>
@@ -6288,8 +6334,12 @@
       <c r="C7" s="50"/>
       <c r="D7" s="50"/>
       <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
+      <c r="F7" s="50" t="s">
+        <v>201</v>
+      </c>
+      <c r="G7" s="50" t="s">
+        <v>201</v>
+      </c>
       <c r="H7" s="51"/>
       <c r="J7" s="52"/>
     </row>
@@ -6359,17 +6409,17 @@
         <v>207</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="79"/>
-      <c r="B12" s="61" t="s">
+    <row r="12" spans="1:11" s="151" customFormat="1" ht="15.75">
+      <c r="A12" s="147"/>
+      <c r="B12" s="153" t="s">
         <v>208</v>
       </c>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="49"/>
+      <c r="C12" s="154"/>
+      <c r="D12" s="154"/>
+      <c r="E12" s="154"/>
+      <c r="F12" s="154"/>
+      <c r="G12" s="154"/>
+      <c r="H12" s="155"/>
     </row>
     <row r="13" spans="1:11" ht="17.100000000000001" thickBot="1">
       <c r="A13" s="79"/>
@@ -6436,18 +6486,20 @@
       <c r="G17" s="72"/>
       <c r="H17" s="49"/>
     </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="79"/>
-      <c r="B18" s="61" t="s">
+    <row r="18" spans="1:10" s="151" customFormat="1" ht="15.75">
+      <c r="A18" s="147"/>
+      <c r="B18" s="153" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="49"/>
-      <c r="J18" s="66"/>
+      <c r="C18" s="154"/>
+      <c r="D18" s="154"/>
+      <c r="E18" s="154"/>
+      <c r="F18" s="154"/>
+      <c r="G18" s="154"/>
+      <c r="H18" s="155"/>
+      <c r="J18" s="156" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="19" spans="1:10" ht="17.100000000000001" thickBot="1">
       <c r="A19" s="79"/>
@@ -6500,13 +6552,13 @@
       <c r="G22" s="72"/>
       <c r="H22" s="49"/>
       <c r="J22" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="79"/>
       <c r="B23" s="61" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C23" s="72"/>
       <c r="D23" s="72"/>
@@ -6527,77 +6579,77 @@
       <c r="G24" s="50"/>
       <c r="H24" s="51"/>
       <c r="J24" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="15.75">
-      <c r="A25" s="79"/>
-      <c r="B25" s="43" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" s="151" customFormat="1" ht="15.75">
+      <c r="A25" s="147"/>
+      <c r="B25" s="148" t="s">
         <v>69</v>
       </c>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="44" t="s">
+      <c r="C25" s="149"/>
+      <c r="D25" s="149"/>
+      <c r="E25" s="149"/>
+      <c r="F25" s="149"/>
+      <c r="G25" s="149"/>
+      <c r="H25" s="150" t="s">
         <v>201</v>
       </c>
-      <c r="J25" s="146" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="15.75">
-      <c r="A26" s="79"/>
-      <c r="B26" s="61" t="s">
+      <c r="J25" s="152" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" s="151" customFormat="1" ht="15.75">
+      <c r="A26" s="147"/>
+      <c r="B26" s="153" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="72"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="72"/>
-      <c r="F26" s="72"/>
-      <c r="G26" s="72"/>
-      <c r="H26" s="49"/>
-      <c r="J26" s="146"/>
-    </row>
-    <row r="27" spans="1:10" ht="15.75">
-      <c r="A27" s="79"/>
-      <c r="B27" s="61" t="s">
+      <c r="C26" s="154"/>
+      <c r="D26" s="154"/>
+      <c r="E26" s="154"/>
+      <c r="F26" s="154"/>
+      <c r="G26" s="154"/>
+      <c r="H26" s="155"/>
+      <c r="J26" s="152"/>
+    </row>
+    <row r="27" spans="1:10" s="151" customFormat="1" ht="15.75">
+      <c r="A27" s="147"/>
+      <c r="B27" s="153" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="72"/>
-      <c r="D27" s="72"/>
-      <c r="E27" s="72"/>
-      <c r="F27" s="72"/>
-      <c r="G27" s="72"/>
-      <c r="H27" s="49"/>
-      <c r="J27" s="146"/>
-    </row>
-    <row r="28" spans="1:10" ht="15.75">
-      <c r="A28" s="79"/>
-      <c r="B28" s="61" t="s">
+      <c r="C27" s="154"/>
+      <c r="D27" s="154"/>
+      <c r="E27" s="154"/>
+      <c r="F27" s="154"/>
+      <c r="G27" s="154"/>
+      <c r="H27" s="155"/>
+      <c r="J27" s="152"/>
+    </row>
+    <row r="28" spans="1:10" s="151" customFormat="1" ht="15.75">
+      <c r="A28" s="147"/>
+      <c r="B28" s="153" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="72"/>
-      <c r="G28" s="72"/>
-      <c r="H28" s="49"/>
-      <c r="J28" s="146"/>
-    </row>
-    <row r="29" spans="1:10" ht="15.75">
-      <c r="A29" s="79"/>
-      <c r="B29" s="61" t="s">
+      <c r="C28" s="154"/>
+      <c r="D28" s="154"/>
+      <c r="E28" s="154"/>
+      <c r="F28" s="154"/>
+      <c r="G28" s="154"/>
+      <c r="H28" s="155"/>
+      <c r="J28" s="152"/>
+    </row>
+    <row r="29" spans="1:10" s="151" customFormat="1" ht="15.75">
+      <c r="A29" s="147"/>
+      <c r="B29" s="153" t="s">
         <v>74</v>
       </c>
-      <c r="C29" s="72"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="72"/>
-      <c r="F29" s="72"/>
-      <c r="G29" s="72"/>
-      <c r="H29" s="49"/>
-      <c r="J29" s="146"/>
+      <c r="C29" s="154"/>
+      <c r="D29" s="154"/>
+      <c r="E29" s="154"/>
+      <c r="F29" s="154"/>
+      <c r="G29" s="154"/>
+      <c r="H29" s="155"/>
+      <c r="J29" s="152"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="79"/>
@@ -6621,7 +6673,7 @@
     <row r="31" spans="1:10">
       <c r="A31" s="79"/>
       <c r="B31" s="61" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C31" s="71"/>
       <c r="D31" s="71"/>
@@ -6634,7 +6686,7 @@
     <row r="32" spans="1:10" ht="17.100000000000001" thickBot="1">
       <c r="A32" s="79"/>
       <c r="B32" s="62" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C32" s="68"/>
       <c r="D32" s="68"/>
@@ -6643,7 +6695,7 @@
       <c r="G32" s="69"/>
       <c r="H32" s="46"/>
       <c r="J32" s="39" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -6668,7 +6720,7 @@
     <row r="34" spans="1:10">
       <c r="A34" s="79"/>
       <c r="B34" s="61" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C34" s="71"/>
       <c r="D34" s="71"/>
@@ -6681,7 +6733,7 @@
     <row r="35" spans="1:10">
       <c r="A35" s="79"/>
       <c r="B35" s="61" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C35" s="71"/>
       <c r="D35" s="71"/>
@@ -6694,7 +6746,7 @@
     <row r="36" spans="1:10" ht="17.100000000000001" thickBot="1">
       <c r="A36" s="80"/>
       <c r="B36" s="62" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C36" s="50"/>
       <c r="D36" s="50"/>
@@ -6715,89 +6767,99 @@
       <c r="E37" s="82" t="s">
         <v>201</v>
       </c>
-      <c r="F37" s="83"/>
+      <c r="F37" s="83" t="s">
+        <v>201</v>
+      </c>
       <c r="G37" s="83"/>
       <c r="H37" s="84"/>
       <c r="J37" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="92"/>
       <c r="B38" s="85" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C38" s="86"/>
       <c r="D38" s="86"/>
       <c r="E38" s="85" t="s">
         <v>201</v>
       </c>
-      <c r="F38" s="86"/>
+      <c r="F38" s="86" t="s">
+        <v>201</v>
+      </c>
       <c r="G38" s="86"/>
       <c r="H38" s="87"/>
       <c r="J38" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="92"/>
       <c r="B39" s="85" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C39" s="86"/>
       <c r="D39" s="86"/>
       <c r="E39" s="85" t="s">
         <v>201</v>
       </c>
-      <c r="F39" s="86"/>
+      <c r="F39" s="86" t="s">
+        <v>201</v>
+      </c>
       <c r="G39" s="86"/>
       <c r="H39" s="87"/>
-      <c r="J39" s="145" t="s">
-        <v>225</v>
+      <c r="J39" s="110" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="17.100000000000001" thickBot="1">
       <c r="A40" s="93"/>
       <c r="B40" s="88" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C40" s="89"/>
       <c r="D40" s="89"/>
       <c r="E40" s="88" t="s">
         <v>201</v>
       </c>
-      <c r="F40" s="89"/>
+      <c r="F40" s="89" t="s">
+        <v>201</v>
+      </c>
       <c r="G40" s="89"/>
       <c r="H40" s="90"/>
       <c r="J40" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="17.100000000000001">
-      <c r="A41" s="107" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="15.75">
+      <c r="A41" s="92"/>
+      <c r="B41" s="85" t="s">
+        <v>229</v>
+      </c>
+      <c r="C41" s="86"/>
+      <c r="D41" s="86"/>
+      <c r="E41" s="85" t="s">
+        <v>201</v>
+      </c>
+      <c r="F41" s="86" t="s">
+        <v>201</v>
+      </c>
+      <c r="G41" s="86"/>
+      <c r="H41" s="86"/>
+    </row>
+    <row r="42" spans="1:10" ht="17.100000000000001">
+      <c r="A42" s="107" t="s">
         <v>152</v>
       </c>
-      <c r="B41" s="40" t="s">
+      <c r="B42" s="40" t="s">
         <v>153</v>
       </c>
-      <c r="C41" s="41"/>
-      <c r="D41" s="105" t="s">
+      <c r="C42" s="41"/>
+      <c r="D42" s="105" t="s">
         <v>201</v>
       </c>
-      <c r="E41" s="41"/>
-      <c r="F41" s="41"/>
-      <c r="G41" s="41"/>
-      <c r="H41" s="41"/>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="108"/>
-      <c r="B42" s="40" t="s">
-        <v>228</v>
-      </c>
-      <c r="C42" s="40" t="s">
-        <v>201</v>
-      </c>
-      <c r="D42" s="41"/>
       <c r="E42" s="41"/>
       <c r="F42" s="41"/>
       <c r="G42" s="41"/>
@@ -6806,7 +6868,7 @@
     <row r="43" spans="1:10">
       <c r="A43" s="108"/>
       <c r="B43" s="40" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C43" s="40" t="s">
         <v>201</v>
@@ -6820,7 +6882,7 @@
     <row r="44" spans="1:10">
       <c r="A44" s="108"/>
       <c r="B44" s="40" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C44" s="40" t="s">
         <v>201</v>
@@ -6833,10 +6895,12 @@
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="108"/>
-      <c r="B45" s="106" t="s">
-        <v>231</v>
-      </c>
-      <c r="C45" s="40"/>
+      <c r="B45" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="C45" s="40" t="s">
+        <v>201</v>
+      </c>
       <c r="D45" s="41"/>
       <c r="E45" s="41"/>
       <c r="F45" s="41"/>
@@ -6846,7 +6910,7 @@
     <row r="46" spans="1:10">
       <c r="A46" s="108"/>
       <c r="B46" s="106" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C46" s="40"/>
       <c r="D46" s="41"/>
@@ -6858,7 +6922,7 @@
     <row r="47" spans="1:10">
       <c r="A47" s="108"/>
       <c r="B47" s="106" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C47" s="40"/>
       <c r="D47" s="41"/>
@@ -6869,22 +6933,20 @@
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="108"/>
-      <c r="B48" s="40" t="s">
-        <v>234</v>
-      </c>
-      <c r="C48" s="40" t="s">
-        <v>201</v>
-      </c>
+      <c r="B48" s="106" t="s">
+        <v>235</v>
+      </c>
+      <c r="C48" s="40"/>
       <c r="D48" s="41"/>
       <c r="E48" s="41"/>
       <c r="F48" s="41"/>
       <c r="G48" s="41"/>
       <c r="H48" s="41"/>
     </row>
-    <row r="49" spans="1:10" ht="17.100000000000001" thickBot="1">
-      <c r="A49" s="109"/>
+    <row r="49" spans="1:10">
+      <c r="A49" s="108"/>
       <c r="B49" s="40" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C49" s="40" t="s">
         <v>201</v>
@@ -6894,64 +6956,82 @@
       <c r="F49" s="41"/>
       <c r="G49" s="41"/>
       <c r="H49" s="41"/>
-      <c r="J49" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="102" t="s">
+      <c r="J49" s="110" t="s">
         <v>237</v>
       </c>
-      <c r="B50" s="101" t="s">
+    </row>
+    <row r="50" spans="1:10" ht="17.100000000000001" thickBot="1">
+      <c r="A50" s="109"/>
+      <c r="B50" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="C50" s="40" t="s">
+        <v>201</v>
+      </c>
+      <c r="D50" s="41"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="41"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="41"/>
+      <c r="J50" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="102" t="s">
+        <v>240</v>
+      </c>
+      <c r="B51" s="101" t="s">
         <v>43</v>
       </c>
-      <c r="C50" s="94"/>
-      <c r="D50" s="94" t="s">
+      <c r="C51" s="94"/>
+      <c r="D51" s="94" t="s">
         <v>201</v>
       </c>
-      <c r="E50" s="94"/>
-      <c r="F50" s="94"/>
-      <c r="G50" s="94"/>
-      <c r="H50" s="95"/>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51" s="103"/>
-      <c r="B51" s="81" t="s">
-        <v>238</v>
-      </c>
-      <c r="C51" s="96"/>
-      <c r="D51" s="96" t="s">
+      <c r="E51" s="94"/>
+      <c r="F51" s="94"/>
+      <c r="G51" s="94" t="s">
         <v>201</v>
       </c>
-      <c r="E51" s="96"/>
-      <c r="F51" s="96"/>
-      <c r="G51" s="96"/>
-      <c r="H51" s="97"/>
-      <c r="J51" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="17.100000000000001" thickBot="1">
-      <c r="A52" s="104"/>
-      <c r="B52" s="98" t="s">
-        <v>240</v>
-      </c>
-      <c r="C52" s="99"/>
-      <c r="D52" s="99"/>
-      <c r="E52" s="99" t="s">
+      <c r="H51" s="95"/>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="103"/>
+      <c r="B52" s="81" t="s">
+        <v>241</v>
+      </c>
+      <c r="C52" s="96"/>
+      <c r="D52" s="96" t="s">
         <v>201</v>
       </c>
-      <c r="F52" s="99"/>
-      <c r="G52" s="99"/>
-      <c r="H52" s="100" t="s">
+      <c r="E52" s="96" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="59" spans="1:10">
-      <c r="B59" s="17"/>
+      <c r="F52" s="96"/>
+      <c r="G52" s="96"/>
+      <c r="H52" s="97"/>
+      <c r="J52" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="17.100000000000001" thickBot="1">
+      <c r="A53" s="104"/>
+      <c r="B53" s="98" t="s">
+        <v>243</v>
+      </c>
+      <c r="C53" s="99"/>
+      <c r="D53" s="99"/>
+      <c r="E53" s="99" t="s">
+        <v>201</v>
+      </c>
+      <c r="F53" s="99"/>
+      <c r="G53" s="99"/>
+      <c r="H53" s="100" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="60" spans="1:10">
-      <c r="B60" s="11"/>
+      <c r="B60" s="17"/>
     </row>
     <row r="61" spans="1:10">
       <c r="B61" s="11"/>
@@ -6959,20 +7039,23 @@
     <row r="62" spans="1:10">
       <c r="B62" s="11"/>
     </row>
-    <row r="63" spans="1:10" ht="17.100000000000001" thickBot="1">
-      <c r="B63" s="19"/>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="17"/>
+    <row r="63" spans="1:10">
+      <c r="B63" s="11"/>
+    </row>
+    <row r="64" spans="1:10" ht="17.100000000000001" thickBot="1">
+      <c r="B64" s="19"/>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="11"/>
+      <c r="A76" s="17"/>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="11"/>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="11"/>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
